--- a/src_files/data_files/TYNDP-2024_National_Trends.xlsx
+++ b/src_files/data_files/TYNDP-2024_National_Trends.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-master\north_european_model\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD589B83-82E9-4843-B962-E92BCFB4F0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{567A6DE8-5628-4257-9441-868CF2783645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="862" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="transferdata" sheetId="15" r:id="rId4"/>
     <sheet name="unittypedata" sheetId="7" r:id="rId5"/>
     <sheet name="emissiondata" sheetId="18" r:id="rId6"/>
-    <sheet name="fueldata" sheetId="17" r:id="rId7"/>
+    <sheet name="nodedata" sheetId="17" r:id="rId7"/>
     <sheet name="trans_capacities" sheetId="16" r:id="rId8"/>
     <sheet name="trans_missing_ref_capacities" sheetId="11" r:id="rId9"/>
     <sheet name="trans_self_loops" sheetId="12" r:id="rId10"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3263" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3267" uniqueCount="216">
   <si>
     <t>Country</t>
   </si>
@@ -859,6 +859,9 @@
   <si>
     <t>transferCap</t>
   </si>
+  <si>
+    <t>nodeBalance</t>
+  </si>
 </sst>
 </file>
 
@@ -1242,10 +1245,7 @@
     <cellStyle name="Normal 5" xfId="2" xr:uid="{3F0C574D-7EC4-4897-89EC-E327150F272B}"/>
     <cellStyle name="Standard_Data provided by OT3" xfId="6" xr:uid="{1E95AE55-13E4-4211-A613-AFC1DB5E5A34}"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="19">
     <dxf>
       <font>
         <b val="0"/>
@@ -1266,51 +1266,6 @@
       </font>
     </dxf>
     <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1327,26 +1282,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
         <scheme val="none"/>
@@ -1478,6 +1413,93 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1502,7 +1524,7 @@
       <sheetName val="data_fuelEmissions"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="4">
           <cell r="E4" t="str">
@@ -1666,7 +1688,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B440C99F-3BB1-4A8C-9867-FC60A58307DE}" name="Table6" displayName="Table6" ref="A1:I1048576" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B440C99F-3BB1-4A8C-9867-FC60A58307DE}" name="Table6" displayName="Table6" ref="A1:I1048576" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
   <autoFilter ref="A1:I1048576" xr:uid="{B440C99F-3BB1-4A8C-9867-FC60A58307DE}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{02926FC6-CA21-44BB-975F-A929C6C412D4}" name="grid"/>
@@ -1684,15 +1706,16 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{D9844F2F-2EE0-434B-9492-0280A28AB057}" name="Table8" displayName="Table8" ref="A1:F21" totalsRowShown="0" headerRowDxfId="8">
-  <autoFilter ref="A1:F21" xr:uid="{D9844F2F-2EE0-434B-9492-0280A28AB057}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{EE76C5C2-E9D6-4CA0-9ABF-B1C7F3426312}" name="Scenario" dataDxfId="7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{D9844F2F-2EE0-434B-9492-0280A28AB057}" name="Table8" displayName="Table8" ref="A1:G22" totalsRowShown="0" headerRowDxfId="18">
+  <autoFilter ref="A1:G22" xr:uid="{D9844F2F-2EE0-434B-9492-0280A28AB057}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{EE76C5C2-E9D6-4CA0-9ABF-B1C7F3426312}" name="Scenario" dataDxfId="17"/>
     <tableColumn id="2" xr3:uid="{40AE79E8-AB14-466F-AE4B-226B9D11277C}" name="Year"/>
-    <tableColumn id="6" xr3:uid="{F58D1D29-CB7C-4B03-8AC3-0955B77DC71F}" name="Country" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{9172289D-E869-498C-9DCD-9CEC866DBBD2}" name="grid" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{AEC998FA-121F-4D1C-B1B1-FC7C7DDBA7AE}" name="price" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{9056A538-46B6-4FAC-AA92-94F33B818677}" name="emission_CO2" dataDxfId="5">
+    <tableColumn id="6" xr3:uid="{F58D1D29-CB7C-4B03-8AC3-0955B77DC71F}" name="Country" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{9172289D-E869-498C-9DCD-9CEC866DBBD2}" name="grid" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{38C23367-B6EA-4644-8FB4-633554D786DA}" name="nodeBalance" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{AEC998FA-121F-4D1C-B1B1-FC7C7DDBA7AE}" name="price" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{9056A538-46B6-4FAC-AA92-94F33B818677}" name="emission_CO2" dataDxfId="15">
       <calculatedColumnFormula>IFERROR(VLOOKUP($D2, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1701,7 +1724,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9719B7EE-3FF9-4612-B637-C2081C2392C1}" name="Table7" displayName="Table7" ref="A1:L93" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9719B7EE-3FF9-4612-B637-C2081C2392C1}" name="Table7" displayName="Table7" ref="A1:L93" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
   <autoFilter ref="A1:L93" xr:uid="{9719B7EE-3FF9-4612-B637-C2081C2392C1}">
     <filterColumn colId="2">
       <filters>
@@ -20054,18 +20077,19 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5703125" style="33" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="28" t="s">
         <v>3</v>
       </c>
@@ -20078,14 +20102,17 @@
       <c r="D1" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="F1" s="29" t="s">
         <v>161</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="G1" s="29" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" s="30" t="s">
         <v>8</v>
       </c>
@@ -20098,15 +20125,16 @@
       <c r="D2" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="E2" s="32">
+      <c r="E2" s="31"/>
+      <c r="F2" s="32">
         <v>27</v>
       </c>
-      <c r="F2" s="33">
+      <c r="G2" s="33">
         <f>IFERROR(VLOOKUP($D2, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.34200000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" s="30" t="s">
         <v>8</v>
       </c>
@@ -20119,15 +20147,16 @@
       <c r="D3" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="32">
+      <c r="E3" s="31"/>
+      <c r="F3" s="32">
         <v>2.5</v>
       </c>
-      <c r="F3" s="33">
+      <c r="G3" s="33">
         <f>IFERROR(VLOOKUP($D3, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7">
       <c r="A4" s="30" t="s">
         <v>8</v>
       </c>
@@ -20140,15 +20169,16 @@
       <c r="D4" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="E4" s="32">
+      <c r="E4" s="31"/>
+      <c r="F4" s="32">
         <v>55</v>
       </c>
-      <c r="F4" s="33">
+      <c r="G4" s="33">
         <f>IFERROR(VLOOKUP($D4, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.19800000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5" s="30" t="s">
         <v>8</v>
       </c>
@@ -20161,15 +20191,16 @@
       <c r="D5" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="31"/>
+      <c r="F5" s="32">
         <v>46</v>
       </c>
-      <c r="F5" s="33">
+      <c r="G5" s="33">
         <f>IFERROR(VLOOKUP($D5, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.28079999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6" s="30" t="s">
         <v>8</v>
       </c>
@@ -20182,15 +20213,16 @@
       <c r="D6" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="31"/>
+      <c r="F6" s="32">
         <v>65</v>
       </c>
-      <c r="F6" s="33">
+      <c r="G6" s="33">
         <f>IFERROR(VLOOKUP($D6, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.25559999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7" s="30" t="s">
         <v>8</v>
       </c>
@@ -20203,15 +20235,16 @@
       <c r="D7" s="31" t="s">
         <v>166</v>
       </c>
-      <c r="E7" s="34">
-        <v>8</v>
-      </c>
-      <c r="F7" s="33">
+      <c r="E7" s="31"/>
+      <c r="F7" s="34">
+        <v>8</v>
+      </c>
+      <c r="G7" s="33">
         <f>IFERROR(VLOOKUP($D7, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.37080000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8" s="30" t="s">
         <v>8</v>
       </c>
@@ -20224,15 +20257,16 @@
       <c r="D8" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="31"/>
+      <c r="F8" s="32">
         <v>26</v>
       </c>
-      <c r="F8" s="33">
+      <c r="G8" s="33">
         <f>IFERROR(VLOOKUP($D8, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9" s="30" t="s">
         <v>8</v>
       </c>
@@ -20245,15 +20279,16 @@
       <c r="D9" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="31"/>
+      <c r="F9" s="33">
         <v>1</v>
       </c>
-      <c r="F9" s="33">
+      <c r="G9" s="33">
         <f>IFERROR(VLOOKUP($D9, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10" s="30" t="s">
         <v>8</v>
       </c>
@@ -20266,15 +20301,16 @@
       <c r="D10" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="31"/>
+      <c r="F10" s="33">
         <v>1</v>
       </c>
-      <c r="F10" s="33">
+      <c r="G10" s="33">
         <f>IFERROR(VLOOKUP($D10, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.14399999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11" s="30" t="s">
         <v>8</v>
       </c>
@@ -20287,15 +20323,15 @@
       <c r="D11" t="s">
         <v>170</v>
       </c>
-      <c r="E11" s="33">
+      <c r="F11" s="33">
         <v>10</v>
       </c>
-      <c r="F11" s="33">
+      <c r="G11" s="33">
         <f>IFERROR(VLOOKUP($D11, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.41399999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:7">
       <c r="A12" s="30" t="s">
         <v>8</v>
       </c>
@@ -20308,15 +20344,16 @@
       <c r="D12" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="31"/>
+      <c r="F12" s="32">
         <v>27</v>
       </c>
-      <c r="F12" s="33">
+      <c r="G12" s="33">
         <f>IFERROR(VLOOKUP($D12, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.34200000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:7">
       <c r="A13" s="30" t="s">
         <v>8</v>
       </c>
@@ -20329,15 +20366,16 @@
       <c r="D13" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="31"/>
+      <c r="F13" s="32">
         <v>2.5</v>
       </c>
-      <c r="F13" s="33">
+      <c r="G13" s="33">
         <f>IFERROR(VLOOKUP($D13, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7">
       <c r="A14" s="30" t="s">
         <v>8</v>
       </c>
@@ -20350,15 +20388,16 @@
       <c r="D14" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="31"/>
+      <c r="F14" s="32">
         <v>55</v>
       </c>
-      <c r="F14" s="33">
+      <c r="G14" s="33">
         <f>IFERROR(VLOOKUP($D14, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.19800000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:7">
       <c r="A15" s="30" t="s">
         <v>8</v>
       </c>
@@ -20371,15 +20410,16 @@
       <c r="D15" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="E15" s="32">
+      <c r="E15" s="31"/>
+      <c r="F15" s="32">
         <v>46</v>
       </c>
-      <c r="F15" s="33">
+      <c r="G15" s="33">
         <f>IFERROR(VLOOKUP($D15, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.28079999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:7">
       <c r="A16" s="30" t="s">
         <v>8</v>
       </c>
@@ -20392,15 +20432,16 @@
       <c r="D16" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="32">
+      <c r="E16" s="31"/>
+      <c r="F16" s="32">
         <v>65</v>
       </c>
-      <c r="F16" s="33">
+      <c r="G16" s="33">
         <f>IFERROR(VLOOKUP($D16, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.25559999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:7">
       <c r="A17" s="30" t="s">
         <v>8</v>
       </c>
@@ -20413,15 +20454,16 @@
       <c r="D17" s="31" t="s">
         <v>166</v>
       </c>
-      <c r="E17" s="34">
-        <v>8</v>
-      </c>
-      <c r="F17" s="33">
+      <c r="E17" s="31"/>
+      <c r="F17" s="34">
+        <v>8</v>
+      </c>
+      <c r="G17" s="33">
         <f>IFERROR(VLOOKUP($D17, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.37080000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:7">
       <c r="A18" s="30" t="s">
         <v>8</v>
       </c>
@@ -20434,15 +20476,16 @@
       <c r="D18" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="E18" s="32">
+      <c r="E18" s="31"/>
+      <c r="F18" s="32">
         <v>26</v>
       </c>
-      <c r="F18" s="33">
+      <c r="G18" s="33">
         <f>IFERROR(VLOOKUP($D18, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:7">
       <c r="A19" s="30" t="s">
         <v>8</v>
       </c>
@@ -20455,15 +20498,16 @@
       <c r="D19" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="E19" s="33">
+      <c r="E19" s="31"/>
+      <c r="F19" s="33">
         <v>1</v>
       </c>
-      <c r="F19" s="33">
+      <c r="G19" s="33">
         <f>IFERROR(VLOOKUP($D19, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:7">
       <c r="A20" s="30" t="s">
         <v>8</v>
       </c>
@@ -20476,15 +20520,16 @@
       <c r="D20" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="31"/>
+      <c r="F20" s="33">
         <v>1</v>
       </c>
-      <c r="F20" s="33">
+      <c r="G20" s="33">
         <f>IFERROR(VLOOKUP($D20, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.14399999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:7">
       <c r="A21" s="30" t="s">
         <v>8</v>
       </c>
@@ -20497,13 +20542,32 @@
       <c r="D21" t="s">
         <v>170</v>
       </c>
-      <c r="E21" s="33">
+      <c r="F21" s="33">
         <v>10</v>
       </c>
-      <c r="F21" s="33">
+      <c r="G21" s="33">
         <f>IFERROR(VLOOKUP($D21, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.41399999999999998</v>
       </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="E22" s="32">
+        <v>1</v>
+      </c>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src_files/data_files/TYNDP-2024_National_Trends.xlsx
+++ b/src_files/data_files/TYNDP-2024_National_Trends.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-master\north_european_model\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{567A6DE8-5628-4257-9441-868CF2783645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19997F16-A474-448F-B428-EAD959E09FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="862" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="862" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="9" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3267" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3266" uniqueCount="215">
   <si>
     <t>Country</t>
   </si>
@@ -342,9 +342,6 @@
   </si>
   <si>
     <t>from_to</t>
-  </si>
-  <si>
-    <t>rampLimit</t>
   </si>
   <si>
     <t xml:space="preserve"> 20231103 - Electricity and Hydrogen Reference Grid &amp; Investment Candidates.xlsx</t>
@@ -1107,7 +1104,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1232,9 +1229,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="ČEPS" xfId="3" xr:uid="{055F4603-C55C-4D73-9C89-501612CA5A5D}"/>
@@ -1246,47 +1240,6 @@
     <cellStyle name="Standard_Data provided by OT3" xfId="6" xr:uid="{1E95AE55-13E4-4211-A613-AFC1DB5E5A34}"/>
   </cellStyles>
   <dxfs count="19">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
     <dxf>
       <border outline="0">
         <top style="thin">
@@ -1479,6 +1432,47 @@
         <charset val="1"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1648,7 +1642,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4481F0AF-41D8-47A8-8506-AC52CB6AB7F9}" name="Table5" displayName="Table5" ref="A1:H616" totalsRowShown="0" headerRowDxfId="14" headerRowBorderDxfId="13" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4481F0AF-41D8-47A8-8506-AC52CB6AB7F9}" name="Table5" displayName="Table5" ref="A1:H616" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9">
   <autoFilter ref="A1:H616" xr:uid="{4481F0AF-41D8-47A8-8506-AC52CB6AB7F9}">
     <filterColumn colId="1">
       <filters>
@@ -1672,7 +1666,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{BE65DD6F-AEBC-42F9-B7B9-FF669064D0A0}" name="Table4" displayName="Table4" ref="A1:G45" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{BE65DD6F-AEBC-42F9-B7B9-FF669064D0A0}" name="Table4" displayName="Table4" ref="A1:G45" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
   <autoFilter ref="A1:G45" xr:uid="{BE65DD6F-AEBC-42F9-B7B9-FF669064D0A0}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{4DDF1ABC-FF46-4BB6-A809-F638501F6746}" name="Country"/>
@@ -1688,16 +1682,15 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B440C99F-3BB1-4A8C-9867-FC60A58307DE}" name="Table6" displayName="Table6" ref="A1:I1048576" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
-  <autoFilter ref="A1:I1048576" xr:uid="{B440C99F-3BB1-4A8C-9867-FC60A58307DE}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B440C99F-3BB1-4A8C-9867-FC60A58307DE}" name="Table6" displayName="Table6" ref="A1:H1048576" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
+  <autoFilter ref="A1:H1048576" xr:uid="{B440C99F-3BB1-4A8C-9867-FC60A58307DE}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{02926FC6-CA21-44BB-975F-A929C6C412D4}" name="grid"/>
     <tableColumn id="2" xr3:uid="{9A1A3B49-8442-4D63-8194-9CB505844700}" name="from_country"/>
     <tableColumn id="3" xr3:uid="{28CF7292-84E4-4FA6-BD4E-4C57CA3CAA7A}" name="to_country"/>
     <tableColumn id="4" xr3:uid="{EFB59F1E-3071-43E4-ACBB-3F295D995CD3}" name="scenario"/>
     <tableColumn id="5" xr3:uid="{8F71BFD3-97D0-464B-A70B-64EFDF49B13C}" name="Year"/>
     <tableColumn id="6" xr3:uid="{F97DCB57-9A9F-4ACB-A684-6295D063A97F}" name="transferCap"/>
-    <tableColumn id="7" xr3:uid="{F818D0F2-31A7-430C-8940-4C3E0C60C88F}" name="rampLimit"/>
     <tableColumn id="8" xr3:uid="{9B30C3ED-0512-4857-96AA-0DDEB6B35219}" name="variableTransCost"/>
     <tableColumn id="9" xr3:uid="{F4413E73-DF9F-4889-9082-448E7A02F911}" name="transferLoss"/>
   </tableColumns>
@@ -1712,10 +1705,10 @@
     <tableColumn id="1" xr3:uid="{EE76C5C2-E9D6-4CA0-9ABF-B1C7F3426312}" name="Scenario" dataDxfId="17"/>
     <tableColumn id="2" xr3:uid="{40AE79E8-AB14-466F-AE4B-226B9D11277C}" name="Year"/>
     <tableColumn id="6" xr3:uid="{F58D1D29-CB7C-4B03-8AC3-0955B77DC71F}" name="Country" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{9172289D-E869-498C-9DCD-9CEC866DBBD2}" name="grid" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{38C23367-B6EA-4644-8FB4-633554D786DA}" name="nodeBalance" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{AEC998FA-121F-4D1C-B1B1-FC7C7DDBA7AE}" name="price" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{9056A538-46B6-4FAC-AA92-94F33B818677}" name="emission_CO2" dataDxfId="15">
+    <tableColumn id="3" xr3:uid="{9172289D-E869-498C-9DCD-9CEC866DBBD2}" name="grid" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{38C23367-B6EA-4644-8FB4-633554D786DA}" name="nodeBalance" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{AEC998FA-121F-4D1C-B1B1-FC7C7DDBA7AE}" name="price" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{9056A538-46B6-4FAC-AA92-94F33B818677}" name="emission_CO2" dataDxfId="12">
       <calculatedColumnFormula>IFERROR(VLOOKUP($D2, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1724,7 +1717,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9719B7EE-3FF9-4612-B637-C2081C2392C1}" name="Table7" displayName="Table7" ref="A1:L93" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9719B7EE-3FF9-4612-B637-C2081C2392C1}" name="Table7" displayName="Table7" ref="A1:L93" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A1:L93" xr:uid="{9719B7EE-3FF9-4612-B637-C2081C2392C1}">
     <filterColumn colId="2">
       <filters>
@@ -2051,21 +2044,21 @@
   <sheetData>
     <row r="1" spans="1:6" ht="180">
       <c r="A1" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="75">
       <c r="A3" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="14"/>
@@ -2075,10 +2068,10 @@
     <row r="4" spans="1:6" ht="30.75" customHeight="1">
       <c r="A4" s="14"/>
       <c r="B4" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
@@ -2087,10 +2080,10 @@
     <row r="5" spans="1:6">
       <c r="A5" s="14"/>
       <c r="B5" s="22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
@@ -2099,10 +2092,10 @@
     <row r="6" spans="1:6" ht="21.75" customHeight="1">
       <c r="A6" s="14"/>
       <c r="B6" s="22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
@@ -2111,10 +2104,10 @@
     <row r="7" spans="1:6" ht="30">
       <c r="A7" s="14"/>
       <c r="B7" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
@@ -2123,10 +2116,10 @@
     <row r="8" spans="1:6" ht="45">
       <c r="A8" s="14"/>
       <c r="B8" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
@@ -2135,10 +2128,10 @@
     <row r="9" spans="1:6" ht="30">
       <c r="A9" s="14"/>
       <c r="B9" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
@@ -2147,10 +2140,10 @@
     <row r="10" spans="1:6" ht="30">
       <c r="A10" s="14"/>
       <c r="B10" s="22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
@@ -2166,10 +2159,10 @@
     </row>
     <row r="12" spans="1:6" ht="60">
       <c r="A12" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
@@ -2186,10 +2179,10 @@
     </row>
     <row r="14" spans="1:6" ht="45">
       <c r="A14" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>175</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
@@ -2213,19 +2206,19 @@
     </row>
     <row r="17" spans="1:6" ht="30">
       <c r="A17" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F17" s="9"/>
     </row>
@@ -2237,13 +2230,13 @@
         <v>28</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="75">
@@ -2254,13 +2247,13 @@
         <v>28</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30">
@@ -2268,16 +2261,16 @@
         <v>3</v>
       </c>
       <c r="B20" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="C20" s="26" t="s">
-        <v>138</v>
-      </c>
       <c r="D20" s="38" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2289,31 +2282,31 @@
     </row>
     <row r="24" spans="1:6" ht="60">
       <c r="A24" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>179</v>
-      </c>
       <c r="C24" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B25" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="B26" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="B27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -2339,10 +2332,10 @@
         <v>90</v>
       </c>
       <c r="B1" s="44" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1" s="44" t="s">
         <v>205</v>
-      </c>
-      <c r="C1" s="44" t="s">
-        <v>206</v>
       </c>
       <c r="D1" s="23" t="s">
         <v>58</v>
@@ -2354,7 +2347,7 @@
         <v>89</v>
       </c>
       <c r="G1" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2366,7 +2359,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D2">
         <v>2030</v>
@@ -2378,7 +2371,7 @@
         <v>1400</v>
       </c>
       <c r="G2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2390,7 +2383,7 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D3">
         <v>2030</v>
@@ -2402,7 +2395,7 @@
         <v>400</v>
       </c>
       <c r="G3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2411,7 +2404,7 @@
         <v>DKBH-DKE1</v>
       </c>
       <c r="B4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -2426,7 +2419,7 @@
         <v>1200</v>
       </c>
       <c r="G4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2438,7 +2431,7 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D5">
         <v>2030</v>
@@ -2450,7 +2443,7 @@
         <v>600</v>
       </c>
       <c r="G5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2462,7 +2455,7 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D6">
         <v>2030</v>
@@ -2474,7 +2467,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2486,7 +2479,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D7">
         <v>2030</v>
@@ -2498,7 +2491,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2510,7 +2503,7 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D8">
         <v>2030</v>
@@ -2522,7 +2515,7 @@
         <v>2000</v>
       </c>
       <c r="G8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2534,7 +2527,7 @@
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D9">
         <v>2030</v>
@@ -2546,7 +2539,7 @@
         <v>400</v>
       </c>
       <c r="G9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2558,7 +2551,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D10">
         <v>2030</v>
@@ -2570,7 +2563,7 @@
         <v>400</v>
       </c>
       <c r="G10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2582,7 +2575,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D11">
         <v>2030</v>
@@ -2594,7 +2587,7 @@
         <v>600</v>
       </c>
       <c r="G11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2606,7 +2599,7 @@
         <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D12">
         <v>2030</v>
@@ -2618,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2627,7 +2620,7 @@
         <v>PL00I-PL00</v>
       </c>
       <c r="B13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C13" t="s">
         <v>22</v>
@@ -2642,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2654,7 +2647,7 @@
         <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D14">
         <v>2030</v>
@@ -2666,7 +2659,7 @@
         <v>400</v>
       </c>
       <c r="G14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2678,7 +2671,7 @@
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D15">
         <v>2040</v>
@@ -2690,7 +2683,7 @@
         <v>3400</v>
       </c>
       <c r="G15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2702,7 +2695,7 @@
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D16">
         <v>2040</v>
@@ -2714,7 +2707,7 @@
         <v>400</v>
       </c>
       <c r="G16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2723,7 +2716,7 @@
         <v>DKBH-DKE1</v>
       </c>
       <c r="B17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -2738,7 +2731,7 @@
         <v>1200</v>
       </c>
       <c r="G17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2750,7 +2743,7 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D18">
         <v>2040</v>
@@ -2762,7 +2755,7 @@
         <v>600</v>
       </c>
       <c r="G18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2774,7 +2767,7 @@
         <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D19">
         <v>2040</v>
@@ -2786,7 +2779,7 @@
         <v>3315.6529999999998</v>
       </c>
       <c r="G19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2798,7 +2791,7 @@
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D20">
         <v>2040</v>
@@ -2810,7 +2803,7 @@
         <v>1330</v>
       </c>
       <c r="G20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2822,7 +2815,7 @@
         <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D21">
         <v>2040</v>
@@ -2834,7 +2827,7 @@
         <v>2000</v>
       </c>
       <c r="G21" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2846,7 +2839,7 @@
         <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D22">
         <v>2040</v>
@@ -2858,7 +2851,7 @@
         <v>1100</v>
       </c>
       <c r="G22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2870,7 +2863,7 @@
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D23">
         <v>2040</v>
@@ -2882,7 +2875,7 @@
         <v>400</v>
       </c>
       <c r="G23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2894,7 +2887,7 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D24">
         <v>2040</v>
@@ -2906,7 +2899,7 @@
         <v>600</v>
       </c>
       <c r="G24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2918,7 +2911,7 @@
         <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D25">
         <v>2040</v>
@@ -2930,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2939,7 +2932,7 @@
         <v>PL00I-PL00</v>
       </c>
       <c r="B26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C26" t="s">
         <v>22</v>
@@ -2954,7 +2947,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2966,7 +2959,7 @@
         <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D27">
         <v>2040</v>
@@ -2978,7 +2971,7 @@
         <v>400</v>
       </c>
       <c r="G27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -3036,10 +3029,10 @@
     </row>
     <row r="2" spans="1:8" hidden="1">
       <c r="A2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -3053,10 +3046,10 @@
     </row>
     <row r="3" spans="1:8" hidden="1">
       <c r="A3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
@@ -3070,10 +3063,10 @@
     </row>
     <row r="4" spans="1:8" hidden="1">
       <c r="A4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -3087,10 +3080,10 @@
     </row>
     <row r="5" spans="1:8" hidden="1">
       <c r="A5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
@@ -3104,7 +3097,7 @@
     </row>
     <row r="6" spans="1:8" hidden="1">
       <c r="A6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B6" t="s">
         <v>36</v>
@@ -3121,7 +3114,7 @@
     </row>
     <row r="7" spans="1:8" hidden="1">
       <c r="A7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B7" t="s">
         <v>42</v>
@@ -3138,7 +3131,7 @@
     </row>
     <row r="8" spans="1:8" hidden="1">
       <c r="A8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B8" t="s">
         <v>43</v>
@@ -3155,7 +3148,7 @@
     </row>
     <row r="9" spans="1:8" hidden="1">
       <c r="A9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B9" t="s">
         <v>45</v>
@@ -3172,7 +3165,7 @@
     </row>
     <row r="10" spans="1:8" hidden="1">
       <c r="A10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B10" t="s">
         <v>38</v>
@@ -3189,7 +3182,7 @@
     </row>
     <row r="11" spans="1:8" hidden="1">
       <c r="A11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B11" t="s">
         <v>37</v>
@@ -3206,7 +3199,7 @@
     </row>
     <row r="12" spans="1:8" hidden="1">
       <c r="A12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B12" t="s">
         <v>44</v>
@@ -3223,7 +3216,7 @@
     </row>
     <row r="13" spans="1:8" hidden="1">
       <c r="A13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B13" t="s">
         <v>41</v>
@@ -3240,7 +3233,7 @@
     </row>
     <row r="14" spans="1:8" hidden="1">
       <c r="A14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B14" t="s">
         <v>35</v>
@@ -3257,10 +3250,10 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C15" t="s">
         <v>8</v>
@@ -3274,10 +3267,10 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C16" t="s">
         <v>8</v>
@@ -3291,7 +3284,7 @@
     </row>
     <row r="17" spans="1:5" hidden="1">
       <c r="A17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s">
         <v>46</v>
@@ -3308,10 +3301,10 @@
     </row>
     <row r="18" spans="1:5" hidden="1">
       <c r="A18" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C18" t="s">
         <v>8</v>
@@ -3325,10 +3318,10 @@
     </row>
     <row r="19" spans="1:5" hidden="1">
       <c r="A19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C19" t="s">
         <v>8</v>
@@ -3342,10 +3335,10 @@
     </row>
     <row r="20" spans="1:5" hidden="1">
       <c r="A20" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C20" t="s">
         <v>8</v>
@@ -3359,10 +3352,10 @@
     </row>
     <row r="21" spans="1:5" hidden="1">
       <c r="A21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C21" t="s">
         <v>8</v>
@@ -3376,10 +3369,10 @@
     </row>
     <row r="22" spans="1:5" hidden="1">
       <c r="A22" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C22" t="s">
         <v>8</v>
@@ -3393,7 +3386,7 @@
     </row>
     <row r="23" spans="1:5" hidden="1">
       <c r="A23" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B23" t="s">
         <v>47</v>
@@ -3410,7 +3403,7 @@
     </row>
     <row r="24" spans="1:5" hidden="1">
       <c r="A24" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B24" t="s">
         <v>40</v>
@@ -3427,10 +3420,10 @@
     </row>
     <row r="25" spans="1:5" hidden="1">
       <c r="A25" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C25" t="s">
         <v>8</v>
@@ -3447,7 +3440,7 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C26" t="s">
         <v>8</v>
@@ -3464,7 +3457,7 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C27" t="s">
         <v>8</v>
@@ -3481,7 +3474,7 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C28" t="s">
         <v>8</v>
@@ -3498,7 +3491,7 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C29" t="s">
         <v>8</v>
@@ -3583,7 +3576,7 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C34" t="s">
         <v>8</v>
@@ -3617,7 +3610,7 @@
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C36" t="s">
         <v>8</v>
@@ -3634,7 +3627,7 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C37" t="s">
         <v>8</v>
@@ -3668,7 +3661,7 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C39" t="s">
         <v>8</v>
@@ -3685,7 +3678,7 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C40" t="s">
         <v>8</v>
@@ -3702,7 +3695,7 @@
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C41" t="s">
         <v>8</v>
@@ -3719,7 +3712,7 @@
         <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C42" t="s">
         <v>8</v>
@@ -3753,7 +3746,7 @@
         <v>6</v>
       </c>
       <c r="B44" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C44" t="s">
         <v>8</v>
@@ -3767,10 +3760,10 @@
     </row>
     <row r="45" spans="1:5" hidden="1">
       <c r="A45" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B45" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C45" t="s">
         <v>8</v>
@@ -3784,10 +3777,10 @@
     </row>
     <row r="46" spans="1:5" hidden="1">
       <c r="A46" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B46" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C46" t="s">
         <v>8</v>
@@ -3801,10 +3794,10 @@
     </row>
     <row r="47" spans="1:5" hidden="1">
       <c r="A47" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B47" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C47" t="s">
         <v>8</v>
@@ -3818,10 +3811,10 @@
     </row>
     <row r="48" spans="1:5" hidden="1">
       <c r="A48" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B48" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C48" t="s">
         <v>8</v>
@@ -3835,10 +3828,10 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C49" t="s">
         <v>8</v>
@@ -3852,10 +3845,10 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C50" t="s">
         <v>8</v>
@@ -3869,7 +3862,7 @@
     </row>
     <row r="51" spans="1:5" hidden="1">
       <c r="A51" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B51" t="s">
         <v>34</v>
@@ -3886,10 +3879,10 @@
     </row>
     <row r="52" spans="1:5" hidden="1">
       <c r="A52" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B52" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C52" t="s">
         <v>8</v>
@@ -3903,10 +3896,10 @@
     </row>
     <row r="53" spans="1:5" hidden="1">
       <c r="A53" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C53" t="s">
         <v>8</v>
@@ -3920,10 +3913,10 @@
     </row>
     <row r="54" spans="1:5" hidden="1">
       <c r="A54" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B54" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C54" t="s">
         <v>8</v>
@@ -3937,10 +3930,10 @@
     </row>
     <row r="55" spans="1:5" hidden="1">
       <c r="A55" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B55" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C55" t="s">
         <v>8</v>
@@ -3954,10 +3947,10 @@
     </row>
     <row r="56" spans="1:5" hidden="1">
       <c r="A56" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B56" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C56" t="s">
         <v>8</v>
@@ -3971,7 +3964,7 @@
     </row>
     <row r="57" spans="1:5" hidden="1">
       <c r="A57" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B57" t="s">
         <v>47</v>
@@ -3988,7 +3981,7 @@
     </row>
     <row r="58" spans="1:5" hidden="1">
       <c r="A58" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B58" t="s">
         <v>40</v>
@@ -4005,10 +3998,10 @@
     </row>
     <row r="59" spans="1:5" hidden="1">
       <c r="A59" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B59" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C59" t="s">
         <v>8</v>
@@ -4025,7 +4018,7 @@
         <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C60" t="s">
         <v>8</v>
@@ -4042,7 +4035,7 @@
         <v>9</v>
       </c>
       <c r="B61" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C61" t="s">
         <v>8</v>
@@ -4059,7 +4052,7 @@
         <v>9</v>
       </c>
       <c r="B62" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C62" t="s">
         <v>8</v>
@@ -4076,7 +4069,7 @@
         <v>9</v>
       </c>
       <c r="B63" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C63" t="s">
         <v>8</v>
@@ -4263,7 +4256,7 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C74" t="s">
         <v>8</v>
@@ -4280,7 +4273,7 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C75" t="s">
         <v>8</v>
@@ -4314,7 +4307,7 @@
         <v>9</v>
       </c>
       <c r="B77" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C77" t="s">
         <v>8</v>
@@ -4331,7 +4324,7 @@
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C78" t="s">
         <v>8</v>
@@ -4348,7 +4341,7 @@
         <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C79" t="s">
         <v>8</v>
@@ -4365,7 +4358,7 @@
         <v>9</v>
       </c>
       <c r="B80" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C80" t="s">
         <v>8</v>
@@ -4382,7 +4375,7 @@
         <v>9</v>
       </c>
       <c r="B81" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C81" t="s">
         <v>8</v>
@@ -4399,7 +4392,7 @@
         <v>9</v>
       </c>
       <c r="B82" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C82" t="s">
         <v>8</v>
@@ -4450,7 +4443,7 @@
         <v>9</v>
       </c>
       <c r="B85" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C85" t="s">
         <v>8</v>
@@ -4467,7 +4460,7 @@
         <v>10</v>
       </c>
       <c r="B86" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C86" t="s">
         <v>8</v>
@@ -4484,7 +4477,7 @@
         <v>10</v>
       </c>
       <c r="B87" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C87" t="s">
         <v>8</v>
@@ -4518,7 +4511,7 @@
         <v>10</v>
       </c>
       <c r="B89" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C89" t="s">
         <v>8</v>
@@ -4569,7 +4562,7 @@
         <v>10</v>
       </c>
       <c r="B92" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C92" t="s">
         <v>8</v>
@@ -4620,7 +4613,7 @@
         <v>10</v>
       </c>
       <c r="B95" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C95" t="s">
         <v>8</v>
@@ -4637,7 +4630,7 @@
         <v>10</v>
       </c>
       <c r="B96" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C96" t="s">
         <v>8</v>
@@ -4654,7 +4647,7 @@
         <v>10</v>
       </c>
       <c r="B97" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C97" t="s">
         <v>8</v>
@@ -4671,7 +4664,7 @@
         <v>11</v>
       </c>
       <c r="B98" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C98" t="s">
         <v>8</v>
@@ -4688,7 +4681,7 @@
         <v>11</v>
       </c>
       <c r="B99" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C99" t="s">
         <v>8</v>
@@ -4705,7 +4698,7 @@
         <v>11</v>
       </c>
       <c r="B100" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C100" t="s">
         <v>8</v>
@@ -4722,7 +4715,7 @@
         <v>11</v>
       </c>
       <c r="B101" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C101" t="s">
         <v>8</v>
@@ -4773,7 +4766,7 @@
         <v>11</v>
       </c>
       <c r="B104" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C104" t="s">
         <v>8</v>
@@ -4858,7 +4851,7 @@
         <v>11</v>
       </c>
       <c r="B109" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C109" t="s">
         <v>8</v>
@@ -4875,7 +4868,7 @@
         <v>11</v>
       </c>
       <c r="B110" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C110" t="s">
         <v>8</v>
@@ -4909,7 +4902,7 @@
         <v>11</v>
       </c>
       <c r="B112" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C112" t="s">
         <v>8</v>
@@ -4926,7 +4919,7 @@
         <v>11</v>
       </c>
       <c r="B113" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C113" t="s">
         <v>8</v>
@@ -4943,7 +4936,7 @@
         <v>11</v>
       </c>
       <c r="B114" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C114" t="s">
         <v>8</v>
@@ -4960,7 +4953,7 @@
         <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C115" t="s">
         <v>8</v>
@@ -4994,7 +4987,7 @@
         <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C117" t="s">
         <v>8</v>
@@ -5011,7 +5004,7 @@
         <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C118" t="s">
         <v>8</v>
@@ -5028,7 +5021,7 @@
         <v>12</v>
       </c>
       <c r="B119" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C119" t="s">
         <v>8</v>
@@ -5062,7 +5055,7 @@
         <v>12</v>
       </c>
       <c r="B121" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C121" t="s">
         <v>8</v>
@@ -5079,7 +5072,7 @@
         <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C122" t="s">
         <v>8</v>
@@ -5096,7 +5089,7 @@
         <v>13</v>
       </c>
       <c r="B123" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C123" t="s">
         <v>8</v>
@@ -5113,7 +5106,7 @@
         <v>13</v>
       </c>
       <c r="B124" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C124" t="s">
         <v>8</v>
@@ -5130,7 +5123,7 @@
         <v>13</v>
       </c>
       <c r="B125" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C125" t="s">
         <v>8</v>
@@ -5147,7 +5140,7 @@
         <v>13</v>
       </c>
       <c r="B126" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C126" t="s">
         <v>8</v>
@@ -5181,7 +5174,7 @@
         <v>13</v>
       </c>
       <c r="B128" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C128" t="s">
         <v>8</v>
@@ -5198,7 +5191,7 @@
         <v>13</v>
       </c>
       <c r="B129" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C129" t="s">
         <v>8</v>
@@ -5232,7 +5225,7 @@
         <v>13</v>
       </c>
       <c r="B131" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C131" t="s">
         <v>8</v>
@@ -5249,7 +5242,7 @@
         <v>13</v>
       </c>
       <c r="B132" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C132" t="s">
         <v>8</v>
@@ -5266,7 +5259,7 @@
         <v>13</v>
       </c>
       <c r="B133" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C133" t="s">
         <v>8</v>
@@ -5283,7 +5276,7 @@
         <v>13</v>
       </c>
       <c r="B134" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C134" t="s">
         <v>8</v>
@@ -5300,7 +5293,7 @@
         <v>13</v>
       </c>
       <c r="B135" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C135" t="s">
         <v>8</v>
@@ -5317,7 +5310,7 @@
         <v>13</v>
       </c>
       <c r="B136" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C136" t="s">
         <v>8</v>
@@ -5368,7 +5361,7 @@
         <v>13</v>
       </c>
       <c r="B139" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C139" t="s">
         <v>8</v>
@@ -5385,7 +5378,7 @@
         <v>13</v>
       </c>
       <c r="B140" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C140" t="s">
         <v>8</v>
@@ -5402,7 +5395,7 @@
         <v>14</v>
       </c>
       <c r="B141" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C141" t="s">
         <v>8</v>
@@ -5419,7 +5412,7 @@
         <v>14</v>
       </c>
       <c r="B142" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C142" t="s">
         <v>8</v>
@@ -5436,7 +5429,7 @@
         <v>14</v>
       </c>
       <c r="B143" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C143" t="s">
         <v>8</v>
@@ -5453,7 +5446,7 @@
         <v>14</v>
       </c>
       <c r="B144" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C144" t="s">
         <v>8</v>
@@ -5555,7 +5548,7 @@
         <v>14</v>
       </c>
       <c r="B150" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C150" t="s">
         <v>8</v>
@@ -5572,7 +5565,7 @@
         <v>14</v>
       </c>
       <c r="B151" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C151" t="s">
         <v>8</v>
@@ -5589,7 +5582,7 @@
         <v>14</v>
       </c>
       <c r="B152" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C152" t="s">
         <v>8</v>
@@ -5623,7 +5616,7 @@
         <v>14</v>
       </c>
       <c r="B154" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C154" t="s">
         <v>8</v>
@@ -5640,7 +5633,7 @@
         <v>14</v>
       </c>
       <c r="B155" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C155" t="s">
         <v>8</v>
@@ -5674,7 +5667,7 @@
         <v>14</v>
       </c>
       <c r="B157" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C157" t="s">
         <v>8</v>
@@ -5691,7 +5684,7 @@
         <v>15</v>
       </c>
       <c r="B158" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C158" t="s">
         <v>8</v>
@@ -5708,7 +5701,7 @@
         <v>15</v>
       </c>
       <c r="B159" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C159" t="s">
         <v>8</v>
@@ -5725,7 +5718,7 @@
         <v>15</v>
       </c>
       <c r="B160" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C160" t="s">
         <v>8</v>
@@ -5742,7 +5735,7 @@
         <v>15</v>
       </c>
       <c r="B161" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C161" t="s">
         <v>8</v>
@@ -5844,7 +5837,7 @@
         <v>15</v>
       </c>
       <c r="B167" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C167" t="s">
         <v>8</v>
@@ -5861,7 +5854,7 @@
         <v>15</v>
       </c>
       <c r="B168" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C168" t="s">
         <v>8</v>
@@ -5912,7 +5905,7 @@
         <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C171" t="s">
         <v>8</v>
@@ -5929,7 +5922,7 @@
         <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C172" t="s">
         <v>8</v>
@@ -5946,7 +5939,7 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C173" t="s">
         <v>8</v>
@@ -5963,7 +5956,7 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C174" t="s">
         <v>8</v>
@@ -5980,7 +5973,7 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C175" t="s">
         <v>8</v>
@@ -5997,7 +5990,7 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C176" t="s">
         <v>8</v>
@@ -6048,7 +6041,7 @@
         <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C179" t="s">
         <v>8</v>
@@ -6065,7 +6058,7 @@
         <v>16</v>
       </c>
       <c r="B180" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C180" t="s">
         <v>8</v>
@@ -6082,7 +6075,7 @@
         <v>16</v>
       </c>
       <c r="B181" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C181" t="s">
         <v>8</v>
@@ -6099,7 +6092,7 @@
         <v>16</v>
       </c>
       <c r="B182" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C182" t="s">
         <v>8</v>
@@ -6116,7 +6109,7 @@
         <v>16</v>
       </c>
       <c r="B183" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C183" t="s">
         <v>8</v>
@@ -6184,7 +6177,7 @@
         <v>16</v>
       </c>
       <c r="B187" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C187" t="s">
         <v>8</v>
@@ -6201,7 +6194,7 @@
         <v>16</v>
       </c>
       <c r="B188" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C188" t="s">
         <v>8</v>
@@ -6218,7 +6211,7 @@
         <v>16</v>
       </c>
       <c r="B189" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C189" t="s">
         <v>8</v>
@@ -6235,7 +6228,7 @@
         <v>16</v>
       </c>
       <c r="B190" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C190" t="s">
         <v>8</v>
@@ -6252,7 +6245,7 @@
         <v>16</v>
       </c>
       <c r="B191" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C191" t="s">
         <v>8</v>
@@ -6269,7 +6262,7 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C192" t="s">
         <v>8</v>
@@ -6303,7 +6296,7 @@
         <v>16</v>
       </c>
       <c r="B194" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C194" t="s">
         <v>8</v>
@@ -6320,7 +6313,7 @@
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C195" t="s">
         <v>8</v>
@@ -6337,7 +6330,7 @@
         <v>17</v>
       </c>
       <c r="B196" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C196" t="s">
         <v>8</v>
@@ -6354,7 +6347,7 @@
         <v>17</v>
       </c>
       <c r="B197" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C197" t="s">
         <v>8</v>
@@ -6405,7 +6398,7 @@
         <v>17</v>
       </c>
       <c r="B200" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C200" t="s">
         <v>8</v>
@@ -6422,7 +6415,7 @@
         <v>17</v>
       </c>
       <c r="B201" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C201" t="s">
         <v>8</v>
@@ -6439,7 +6432,7 @@
         <v>17</v>
       </c>
       <c r="B202" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C202" t="s">
         <v>8</v>
@@ -6473,7 +6466,7 @@
         <v>17</v>
       </c>
       <c r="B204" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C204" t="s">
         <v>8</v>
@@ -6490,7 +6483,7 @@
         <v>17</v>
       </c>
       <c r="B205" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C205" t="s">
         <v>8</v>
@@ -6507,7 +6500,7 @@
         <v>18</v>
       </c>
       <c r="B206" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C206" t="s">
         <v>8</v>
@@ -6524,7 +6517,7 @@
         <v>18</v>
       </c>
       <c r="B207" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C207" t="s">
         <v>8</v>
@@ -6541,7 +6534,7 @@
         <v>18</v>
       </c>
       <c r="B208" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C208" t="s">
         <v>8</v>
@@ -6558,7 +6551,7 @@
         <v>18</v>
       </c>
       <c r="B209" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C209" t="s">
         <v>8</v>
@@ -6660,7 +6653,7 @@
         <v>18</v>
       </c>
       <c r="B215" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C215" t="s">
         <v>8</v>
@@ -6677,7 +6670,7 @@
         <v>18</v>
       </c>
       <c r="B216" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C216" t="s">
         <v>8</v>
@@ -6711,7 +6704,7 @@
         <v>18</v>
       </c>
       <c r="B218" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C218" t="s">
         <v>8</v>
@@ -6728,7 +6721,7 @@
         <v>18</v>
       </c>
       <c r="B219" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C219" t="s">
         <v>8</v>
@@ -6762,7 +6755,7 @@
         <v>18</v>
       </c>
       <c r="B221" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C221" t="s">
         <v>8</v>
@@ -6779,7 +6772,7 @@
         <v>19</v>
       </c>
       <c r="B222" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C222" t="s">
         <v>8</v>
@@ -6796,7 +6789,7 @@
         <v>19</v>
       </c>
       <c r="B223" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C223" t="s">
         <v>8</v>
@@ -6813,7 +6806,7 @@
         <v>19</v>
       </c>
       <c r="B224" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C224" t="s">
         <v>8</v>
@@ -6830,7 +6823,7 @@
         <v>19</v>
       </c>
       <c r="B225" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C225" t="s">
         <v>8</v>
@@ -6847,7 +6840,7 @@
         <v>19</v>
       </c>
       <c r="B226" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C226" t="s">
         <v>8</v>
@@ -6864,7 +6857,7 @@
         <v>19</v>
       </c>
       <c r="B227" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C227" t="s">
         <v>8</v>
@@ -6881,7 +6874,7 @@
         <v>20</v>
       </c>
       <c r="B228" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C228" t="s">
         <v>8</v>
@@ -6898,7 +6891,7 @@
         <v>20</v>
       </c>
       <c r="B229" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C229" t="s">
         <v>8</v>
@@ -6915,7 +6908,7 @@
         <v>20</v>
       </c>
       <c r="B230" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C230" t="s">
         <v>8</v>
@@ -6932,7 +6925,7 @@
         <v>20</v>
       </c>
       <c r="B231" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C231" t="s">
         <v>8</v>
@@ -6949,7 +6942,7 @@
         <v>20</v>
       </c>
       <c r="B232" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C232" t="s">
         <v>8</v>
@@ -6966,7 +6959,7 @@
         <v>21</v>
       </c>
       <c r="B233" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C233" t="s">
         <v>8</v>
@@ -6983,7 +6976,7 @@
         <v>21</v>
       </c>
       <c r="B234" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C234" t="s">
         <v>8</v>
@@ -7000,7 +6993,7 @@
         <v>21</v>
       </c>
       <c r="B235" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C235" t="s">
         <v>8</v>
@@ -7017,7 +7010,7 @@
         <v>21</v>
       </c>
       <c r="B236" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C236" t="s">
         <v>8</v>
@@ -7034,7 +7027,7 @@
         <v>21</v>
       </c>
       <c r="B237" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C237" t="s">
         <v>8</v>
@@ -7051,7 +7044,7 @@
         <v>21</v>
       </c>
       <c r="B238" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C238" t="s">
         <v>8</v>
@@ -7068,7 +7061,7 @@
         <v>21</v>
       </c>
       <c r="B239" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C239" t="s">
         <v>8</v>
@@ -7085,7 +7078,7 @@
         <v>21</v>
       </c>
       <c r="B240" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C240" t="s">
         <v>8</v>
@@ -7102,7 +7095,7 @@
         <v>22</v>
       </c>
       <c r="B241" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C241" t="s">
         <v>8</v>
@@ -7153,7 +7146,7 @@
         <v>22</v>
       </c>
       <c r="B244" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C244" t="s">
         <v>8</v>
@@ -7221,7 +7214,7 @@
         <v>22</v>
       </c>
       <c r="B248" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C248" t="s">
         <v>8</v>
@@ -7238,7 +7231,7 @@
         <v>22</v>
       </c>
       <c r="B249" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C249" t="s">
         <v>8</v>
@@ -7289,7 +7282,7 @@
         <v>22</v>
       </c>
       <c r="B252" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C252" t="s">
         <v>8</v>
@@ -7306,7 +7299,7 @@
         <v>22</v>
       </c>
       <c r="B253" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C253" t="s">
         <v>8</v>
@@ -7323,7 +7316,7 @@
         <v>22</v>
       </c>
       <c r="B254" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C254" t="s">
         <v>8</v>
@@ -7340,7 +7333,7 @@
         <v>22</v>
       </c>
       <c r="B255" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C255" t="s">
         <v>8</v>
@@ -7357,7 +7350,7 @@
         <v>22</v>
       </c>
       <c r="B256" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C256" t="s">
         <v>8</v>
@@ -7374,7 +7367,7 @@
         <v>22</v>
       </c>
       <c r="B257" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C257" t="s">
         <v>8</v>
@@ -7425,7 +7418,7 @@
         <v>22</v>
       </c>
       <c r="B260" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C260" t="s">
         <v>8</v>
@@ -7442,7 +7435,7 @@
         <v>23</v>
       </c>
       <c r="B261" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C261" t="s">
         <v>8</v>
@@ -7459,7 +7452,7 @@
         <v>23</v>
       </c>
       <c r="B262" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C262" t="s">
         <v>8</v>
@@ -7476,7 +7469,7 @@
         <v>23</v>
       </c>
       <c r="B263" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C263" t="s">
         <v>8</v>
@@ -7493,7 +7486,7 @@
         <v>23</v>
       </c>
       <c r="B264" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C264" t="s">
         <v>8</v>
@@ -7527,7 +7520,7 @@
         <v>23</v>
       </c>
       <c r="B266" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C266" t="s">
         <v>8</v>
@@ -7544,7 +7537,7 @@
         <v>23</v>
       </c>
       <c r="B267" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C267" t="s">
         <v>8</v>
@@ -7578,7 +7571,7 @@
         <v>24</v>
       </c>
       <c r="B269" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C269" t="s">
         <v>8</v>
@@ -7595,7 +7588,7 @@
         <v>24</v>
       </c>
       <c r="B270" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C270" t="s">
         <v>8</v>
@@ -7612,7 +7605,7 @@
         <v>24</v>
       </c>
       <c r="B271" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C271" t="s">
         <v>8</v>
@@ -7629,7 +7622,7 @@
         <v>24</v>
       </c>
       <c r="B272" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C272" t="s">
         <v>8</v>
@@ -7646,7 +7639,7 @@
         <v>24</v>
       </c>
       <c r="B273" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C273" t="s">
         <v>8</v>
@@ -7663,7 +7656,7 @@
         <v>24</v>
       </c>
       <c r="B274" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C274" t="s">
         <v>8</v>
@@ -7697,7 +7690,7 @@
         <v>24</v>
       </c>
       <c r="B276" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C276" t="s">
         <v>8</v>
@@ -7714,7 +7707,7 @@
         <v>25</v>
       </c>
       <c r="B277" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C277" t="s">
         <v>8</v>
@@ -7731,7 +7724,7 @@
         <v>25</v>
       </c>
       <c r="B278" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C278" t="s">
         <v>8</v>
@@ -7748,7 +7741,7 @@
         <v>25</v>
       </c>
       <c r="B279" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C279" t="s">
         <v>8</v>
@@ -7765,7 +7758,7 @@
         <v>25</v>
       </c>
       <c r="B280" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C280" t="s">
         <v>8</v>
@@ -7799,7 +7792,7 @@
         <v>25</v>
       </c>
       <c r="B282" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C282" t="s">
         <v>8</v>
@@ -7833,7 +7826,7 @@
         <v>25</v>
       </c>
       <c r="B284" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C284" t="s">
         <v>8</v>
@@ -7867,7 +7860,7 @@
         <v>25</v>
       </c>
       <c r="B286" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C286" t="s">
         <v>8</v>
@@ -7884,7 +7877,7 @@
         <v>26</v>
       </c>
       <c r="B287" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C287" t="s">
         <v>8</v>
@@ -7901,7 +7894,7 @@
         <v>26</v>
       </c>
       <c r="B288" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C288" t="s">
         <v>8</v>
@@ -7918,7 +7911,7 @@
         <v>26</v>
       </c>
       <c r="B289" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C289" t="s">
         <v>8</v>
@@ -7935,7 +7928,7 @@
         <v>26</v>
       </c>
       <c r="B290" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C290" t="s">
         <v>8</v>
@@ -7952,7 +7945,7 @@
         <v>26</v>
       </c>
       <c r="B291" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C291" t="s">
         <v>8</v>
@@ -7969,7 +7962,7 @@
         <v>26</v>
       </c>
       <c r="B292" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C292" t="s">
         <v>8</v>
@@ -7986,7 +7979,7 @@
         <v>26</v>
       </c>
       <c r="B293" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C293" t="s">
         <v>8</v>
@@ -8020,7 +8013,7 @@
         <v>26</v>
       </c>
       <c r="B295" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C295" t="s">
         <v>8</v>
@@ -8037,7 +8030,7 @@
         <v>27</v>
       </c>
       <c r="B296" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C296" t="s">
         <v>8</v>
@@ -8054,7 +8047,7 @@
         <v>27</v>
       </c>
       <c r="B297" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C297" t="s">
         <v>8</v>
@@ -8071,7 +8064,7 @@
         <v>27</v>
       </c>
       <c r="B298" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C298" t="s">
         <v>8</v>
@@ -8088,7 +8081,7 @@
         <v>27</v>
       </c>
       <c r="B299" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C299" t="s">
         <v>8</v>
@@ -8275,7 +8268,7 @@
         <v>27</v>
       </c>
       <c r="B310" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C310" t="s">
         <v>8</v>
@@ -8292,7 +8285,7 @@
         <v>27</v>
       </c>
       <c r="B311" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C311" t="s">
         <v>8</v>
@@ -8326,7 +8319,7 @@
         <v>27</v>
       </c>
       <c r="B313" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C313" t="s">
         <v>8</v>
@@ -8360,7 +8353,7 @@
         <v>27</v>
       </c>
       <c r="B315" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C315" t="s">
         <v>8</v>
@@ -8377,7 +8370,7 @@
         <v>27</v>
       </c>
       <c r="B316" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C316" t="s">
         <v>8</v>
@@ -8394,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="B317" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C317" t="s">
         <v>8</v>
@@ -8411,7 +8404,7 @@
         <v>27</v>
       </c>
       <c r="B318" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C318" t="s">
         <v>8</v>
@@ -8445,7 +8438,7 @@
         <v>27</v>
       </c>
       <c r="B320" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C320" t="s">
         <v>8</v>
@@ -8459,10 +8452,10 @@
     </row>
     <row r="321" spans="1:5" hidden="1">
       <c r="A321" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B321" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C321" t="s">
         <v>8</v>
@@ -8476,10 +8469,10 @@
     </row>
     <row r="322" spans="1:5" hidden="1">
       <c r="A322" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B322" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C322" t="s">
         <v>8</v>
@@ -8493,10 +8486,10 @@
     </row>
     <row r="323" spans="1:5" hidden="1">
       <c r="A323" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B323" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C323" t="s">
         <v>8</v>
@@ -8510,10 +8503,10 @@
     </row>
     <row r="324" spans="1:5" hidden="1">
       <c r="A324" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B324" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C324" t="s">
         <v>8</v>
@@ -8527,7 +8520,7 @@
     </row>
     <row r="325" spans="1:5" hidden="1">
       <c r="A325" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B325" t="s">
         <v>48</v>
@@ -8544,10 +8537,10 @@
     </row>
     <row r="326" spans="1:5">
       <c r="A326" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B326" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C326" t="s">
         <v>8</v>
@@ -8561,10 +8554,10 @@
     </row>
     <row r="327" spans="1:5">
       <c r="A327" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B327" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C327" t="s">
         <v>8</v>
@@ -8578,10 +8571,10 @@
     </row>
     <row r="328" spans="1:5" hidden="1">
       <c r="A328" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B328" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C328" t="s">
         <v>8</v>
@@ -8595,10 +8588,10 @@
     </row>
     <row r="329" spans="1:5" hidden="1">
       <c r="A329" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B329" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C329" t="s">
         <v>8</v>
@@ -8612,10 +8605,10 @@
     </row>
     <row r="330" spans="1:5" hidden="1">
       <c r="A330" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B330" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C330" t="s">
         <v>8</v>
@@ -8629,10 +8622,10 @@
     </row>
     <row r="331" spans="1:5" hidden="1">
       <c r="A331" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B331" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C331" t="s">
         <v>8</v>
@@ -8646,10 +8639,10 @@
     </row>
     <row r="332" spans="1:5" hidden="1">
       <c r="A332" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B332" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C332" t="s">
         <v>8</v>
@@ -8663,7 +8656,7 @@
     </row>
     <row r="333" spans="1:5" hidden="1">
       <c r="A333" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B333" t="s">
         <v>47</v>
@@ -8680,7 +8673,7 @@
     </row>
     <row r="334" spans="1:5" hidden="1">
       <c r="A334" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B334" t="s">
         <v>40</v>
@@ -8697,10 +8690,10 @@
     </row>
     <row r="335" spans="1:5" hidden="1">
       <c r="A335" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B335" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C335" t="s">
         <v>8</v>
@@ -8717,7 +8710,7 @@
         <v>6</v>
       </c>
       <c r="B336" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C336" t="s">
         <v>8</v>
@@ -8734,7 +8727,7 @@
         <v>6</v>
       </c>
       <c r="B337" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C337" t="s">
         <v>8</v>
@@ -8751,7 +8744,7 @@
         <v>6</v>
       </c>
       <c r="B338" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C338" t="s">
         <v>8</v>
@@ -8768,7 +8761,7 @@
         <v>6</v>
       </c>
       <c r="B339" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C339" t="s">
         <v>8</v>
@@ -8836,7 +8829,7 @@
         <v>6</v>
       </c>
       <c r="B343" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C343" t="s">
         <v>8</v>
@@ -8887,7 +8880,7 @@
         <v>6</v>
       </c>
       <c r="B346" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C346" t="s">
         <v>8</v>
@@ -8904,7 +8897,7 @@
         <v>6</v>
       </c>
       <c r="B347" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C347" t="s">
         <v>8</v>
@@ -8921,7 +8914,7 @@
         <v>6</v>
       </c>
       <c r="B348" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C348" t="s">
         <v>8</v>
@@ -8938,7 +8931,7 @@
         <v>6</v>
       </c>
       <c r="B349" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C349" t="s">
         <v>8</v>
@@ -8955,7 +8948,7 @@
         <v>6</v>
       </c>
       <c r="B350" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C350" t="s">
         <v>8</v>
@@ -8972,7 +8965,7 @@
         <v>6</v>
       </c>
       <c r="B351" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C351" t="s">
         <v>8</v>
@@ -9006,7 +8999,7 @@
         <v>6</v>
       </c>
       <c r="B353" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C353" t="s">
         <v>8</v>
@@ -9020,10 +9013,10 @@
     </row>
     <row r="354" spans="1:5" hidden="1">
       <c r="A354" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B354" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C354" t="s">
         <v>8</v>
@@ -9037,10 +9030,10 @@
     </row>
     <row r="355" spans="1:5" hidden="1">
       <c r="A355" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B355" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C355" t="s">
         <v>8</v>
@@ -9054,10 +9047,10 @@
     </row>
     <row r="356" spans="1:5" hidden="1">
       <c r="A356" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B356" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C356" t="s">
         <v>8</v>
@@ -9071,10 +9064,10 @@
     </row>
     <row r="357" spans="1:5" hidden="1">
       <c r="A357" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B357" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C357" t="s">
         <v>8</v>
@@ -9088,10 +9081,10 @@
     </row>
     <row r="358" spans="1:5">
       <c r="A358" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B358" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C358" t="s">
         <v>8</v>
@@ -9105,10 +9098,10 @@
     </row>
     <row r="359" spans="1:5">
       <c r="A359" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B359" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C359" t="s">
         <v>8</v>
@@ -9122,10 +9115,10 @@
     </row>
     <row r="360" spans="1:5" hidden="1">
       <c r="A360" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B360" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C360" t="s">
         <v>8</v>
@@ -9139,10 +9132,10 @@
     </row>
     <row r="361" spans="1:5" hidden="1">
       <c r="A361" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B361" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C361" t="s">
         <v>8</v>
@@ -9156,10 +9149,10 @@
     </row>
     <row r="362" spans="1:5" hidden="1">
       <c r="A362" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B362" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C362" t="s">
         <v>8</v>
@@ -9173,10 +9166,10 @@
     </row>
     <row r="363" spans="1:5" hidden="1">
       <c r="A363" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B363" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C363" t="s">
         <v>8</v>
@@ -9190,10 +9183,10 @@
     </row>
     <row r="364" spans="1:5" hidden="1">
       <c r="A364" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B364" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C364" t="s">
         <v>8</v>
@@ -9207,7 +9200,7 @@
     </row>
     <row r="365" spans="1:5" hidden="1">
       <c r="A365" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B365" t="s">
         <v>47</v>
@@ -9224,7 +9217,7 @@
     </row>
     <row r="366" spans="1:5" hidden="1">
       <c r="A366" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B366" t="s">
         <v>40</v>
@@ -9241,10 +9234,10 @@
     </row>
     <row r="367" spans="1:5" hidden="1">
       <c r="A367" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B367" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C367" t="s">
         <v>8</v>
@@ -9261,7 +9254,7 @@
         <v>9</v>
       </c>
       <c r="B368" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C368" t="s">
         <v>8</v>
@@ -9278,7 +9271,7 @@
         <v>9</v>
       </c>
       <c r="B369" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C369" t="s">
         <v>8</v>
@@ -9295,7 +9288,7 @@
         <v>9</v>
       </c>
       <c r="B370" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C370" t="s">
         <v>8</v>
@@ -9312,7 +9305,7 @@
         <v>9</v>
       </c>
       <c r="B371" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C371" t="s">
         <v>8</v>
@@ -9448,7 +9441,7 @@
         <v>9</v>
       </c>
       <c r="B379" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C379" t="s">
         <v>8</v>
@@ -9465,7 +9458,7 @@
         <v>9</v>
       </c>
       <c r="B380" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C380" t="s">
         <v>8</v>
@@ -9482,7 +9475,7 @@
         <v>9</v>
       </c>
       <c r="B381" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C381" t="s">
         <v>8</v>
@@ -9499,7 +9492,7 @@
         <v>9</v>
       </c>
       <c r="B382" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C382" t="s">
         <v>8</v>
@@ -9516,7 +9509,7 @@
         <v>9</v>
       </c>
       <c r="B383" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C383" t="s">
         <v>8</v>
@@ -9533,7 +9526,7 @@
         <v>9</v>
       </c>
       <c r="B384" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C384" t="s">
         <v>8</v>
@@ -9550,7 +9543,7 @@
         <v>9</v>
       </c>
       <c r="B385" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C385" t="s">
         <v>8</v>
@@ -9567,7 +9560,7 @@
         <v>9</v>
       </c>
       <c r="B386" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C386" t="s">
         <v>8</v>
@@ -9618,7 +9611,7 @@
         <v>9</v>
       </c>
       <c r="B389" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C389" t="s">
         <v>8</v>
@@ -9635,7 +9628,7 @@
         <v>10</v>
       </c>
       <c r="B390" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C390" t="s">
         <v>8</v>
@@ -9652,7 +9645,7 @@
         <v>10</v>
       </c>
       <c r="B391" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C391" t="s">
         <v>8</v>
@@ -9669,7 +9662,7 @@
         <v>10</v>
       </c>
       <c r="B392" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C392" t="s">
         <v>8</v>
@@ -9720,7 +9713,7 @@
         <v>10</v>
       </c>
       <c r="B395" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C395" t="s">
         <v>8</v>
@@ -9771,7 +9764,7 @@
         <v>10</v>
       </c>
       <c r="B398" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C398" t="s">
         <v>8</v>
@@ -9788,7 +9781,7 @@
         <v>10</v>
       </c>
       <c r="B399" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C399" t="s">
         <v>8</v>
@@ -9805,7 +9798,7 @@
         <v>10</v>
       </c>
       <c r="B400" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C400" t="s">
         <v>8</v>
@@ -9822,7 +9815,7 @@
         <v>11</v>
       </c>
       <c r="B401" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C401" t="s">
         <v>8</v>
@@ -9839,7 +9832,7 @@
         <v>11</v>
       </c>
       <c r="B402" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C402" t="s">
         <v>8</v>
@@ -9856,7 +9849,7 @@
         <v>11</v>
       </c>
       <c r="B403" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C403" t="s">
         <v>8</v>
@@ -9873,7 +9866,7 @@
         <v>11</v>
       </c>
       <c r="B404" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C404" t="s">
         <v>8</v>
@@ -9907,7 +9900,7 @@
         <v>11</v>
       </c>
       <c r="B406" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C406" t="s">
         <v>8</v>
@@ -9958,7 +9951,7 @@
         <v>11</v>
       </c>
       <c r="B409" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C409" t="s">
         <v>8</v>
@@ -9975,7 +9968,7 @@
         <v>11</v>
       </c>
       <c r="B410" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C410" t="s">
         <v>8</v>
@@ -10009,7 +10002,7 @@
         <v>11</v>
       </c>
       <c r="B412" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C412" t="s">
         <v>8</v>
@@ -10026,7 +10019,7 @@
         <v>11</v>
       </c>
       <c r="B413" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C413" t="s">
         <v>8</v>
@@ -10043,7 +10036,7 @@
         <v>11</v>
       </c>
       <c r="B414" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C414" t="s">
         <v>8</v>
@@ -10060,7 +10053,7 @@
         <v>12</v>
       </c>
       <c r="B415" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C415" t="s">
         <v>8</v>
@@ -10094,7 +10087,7 @@
         <v>12</v>
       </c>
       <c r="B417" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C417" t="s">
         <v>8</v>
@@ -10111,7 +10104,7 @@
         <v>12</v>
       </c>
       <c r="B418" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C418" t="s">
         <v>8</v>
@@ -10128,7 +10121,7 @@
         <v>12</v>
       </c>
       <c r="B419" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C419" t="s">
         <v>8</v>
@@ -10145,7 +10138,7 @@
         <v>12</v>
       </c>
       <c r="B420" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C420" t="s">
         <v>8</v>
@@ -10162,7 +10155,7 @@
         <v>12</v>
       </c>
       <c r="B421" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C421" t="s">
         <v>8</v>
@@ -10179,7 +10172,7 @@
         <v>12</v>
       </c>
       <c r="B422" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C422" t="s">
         <v>8</v>
@@ -10196,7 +10189,7 @@
         <v>13</v>
       </c>
       <c r="B423" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C423" t="s">
         <v>8</v>
@@ -10213,7 +10206,7 @@
         <v>13</v>
       </c>
       <c r="B424" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C424" t="s">
         <v>8</v>
@@ -10230,7 +10223,7 @@
         <v>13</v>
       </c>
       <c r="B425" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C425" t="s">
         <v>8</v>
@@ -10247,7 +10240,7 @@
         <v>13</v>
       </c>
       <c r="B426" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C426" t="s">
         <v>8</v>
@@ -10281,7 +10274,7 @@
         <v>13</v>
       </c>
       <c r="B428" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C428" t="s">
         <v>8</v>
@@ -10298,7 +10291,7 @@
         <v>13</v>
       </c>
       <c r="B429" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C429" t="s">
         <v>8</v>
@@ -10315,7 +10308,7 @@
         <v>13</v>
       </c>
       <c r="B430" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C430" t="s">
         <v>8</v>
@@ -10332,7 +10325,7 @@
         <v>13</v>
       </c>
       <c r="B431" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C431" t="s">
         <v>8</v>
@@ -10349,7 +10342,7 @@
         <v>13</v>
       </c>
       <c r="B432" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C432" t="s">
         <v>8</v>
@@ -10366,7 +10359,7 @@
         <v>13</v>
       </c>
       <c r="B433" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C433" t="s">
         <v>8</v>
@@ -10383,7 +10376,7 @@
         <v>13</v>
       </c>
       <c r="B434" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C434" t="s">
         <v>8</v>
@@ -10400,7 +10393,7 @@
         <v>13</v>
       </c>
       <c r="B435" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C435" t="s">
         <v>8</v>
@@ -10451,7 +10444,7 @@
         <v>13</v>
       </c>
       <c r="B438" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C438" t="s">
         <v>8</v>
@@ -10468,7 +10461,7 @@
         <v>13</v>
       </c>
       <c r="B439" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C439" t="s">
         <v>8</v>
@@ -10485,7 +10478,7 @@
         <v>14</v>
       </c>
       <c r="B440" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C440" t="s">
         <v>8</v>
@@ -10502,7 +10495,7 @@
         <v>14</v>
       </c>
       <c r="B441" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C441" t="s">
         <v>8</v>
@@ -10519,7 +10512,7 @@
         <v>14</v>
       </c>
       <c r="B442" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C442" t="s">
         <v>8</v>
@@ -10536,7 +10529,7 @@
         <v>14</v>
       </c>
       <c r="B443" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C443" t="s">
         <v>8</v>
@@ -10621,7 +10614,7 @@
         <v>14</v>
       </c>
       <c r="B448" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C448" t="s">
         <v>8</v>
@@ -10638,7 +10631,7 @@
         <v>14</v>
       </c>
       <c r="B449" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C449" t="s">
         <v>8</v>
@@ -10655,7 +10648,7 @@
         <v>14</v>
       </c>
       <c r="B450" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C450" t="s">
         <v>8</v>
@@ -10689,7 +10682,7 @@
         <v>14</v>
       </c>
       <c r="B452" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C452" t="s">
         <v>8</v>
@@ -10706,7 +10699,7 @@
         <v>14</v>
       </c>
       <c r="B453" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C453" t="s">
         <v>8</v>
@@ -10740,7 +10733,7 @@
         <v>14</v>
       </c>
       <c r="B455" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C455" t="s">
         <v>8</v>
@@ -10757,7 +10750,7 @@
         <v>15</v>
       </c>
       <c r="B456" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C456" t="s">
         <v>8</v>
@@ -10774,7 +10767,7 @@
         <v>15</v>
       </c>
       <c r="B457" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C457" t="s">
         <v>8</v>
@@ -10791,7 +10784,7 @@
         <v>15</v>
       </c>
       <c r="B458" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C458" t="s">
         <v>8</v>
@@ -10808,7 +10801,7 @@
         <v>15</v>
       </c>
       <c r="B459" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C459" t="s">
         <v>8</v>
@@ -10876,7 +10869,7 @@
         <v>15</v>
       </c>
       <c r="B463" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C463" t="s">
         <v>8</v>
@@ -10893,7 +10886,7 @@
         <v>15</v>
       </c>
       <c r="B464" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C464" t="s">
         <v>8</v>
@@ -10944,7 +10937,7 @@
         <v>15</v>
       </c>
       <c r="B467" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C467" t="s">
         <v>8</v>
@@ -10961,7 +10954,7 @@
         <v>15</v>
       </c>
       <c r="B468" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C468" t="s">
         <v>8</v>
@@ -10978,7 +10971,7 @@
         <v>15</v>
       </c>
       <c r="B469" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C469" t="s">
         <v>8</v>
@@ -10995,7 +10988,7 @@
         <v>15</v>
       </c>
       <c r="B470" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C470" t="s">
         <v>8</v>
@@ -11012,7 +11005,7 @@
         <v>15</v>
       </c>
       <c r="B471" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C471" t="s">
         <v>8</v>
@@ -11029,7 +11022,7 @@
         <v>15</v>
       </c>
       <c r="B472" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C472" t="s">
         <v>8</v>
@@ -11080,7 +11073,7 @@
         <v>15</v>
       </c>
       <c r="B475" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C475" t="s">
         <v>8</v>
@@ -11097,7 +11090,7 @@
         <v>16</v>
       </c>
       <c r="B476" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C476" t="s">
         <v>8</v>
@@ -11114,7 +11107,7 @@
         <v>16</v>
       </c>
       <c r="B477" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C477" t="s">
         <v>8</v>
@@ -11131,7 +11124,7 @@
         <v>16</v>
       </c>
       <c r="B478" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C478" t="s">
         <v>8</v>
@@ -11148,7 +11141,7 @@
         <v>16</v>
       </c>
       <c r="B479" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C479" t="s">
         <v>8</v>
@@ -11199,7 +11192,7 @@
         <v>16</v>
       </c>
       <c r="B482" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C482" t="s">
         <v>8</v>
@@ -11216,7 +11209,7 @@
         <v>16</v>
       </c>
       <c r="B483" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C483" t="s">
         <v>8</v>
@@ -11233,7 +11226,7 @@
         <v>16</v>
       </c>
       <c r="B484" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C484" t="s">
         <v>8</v>
@@ -11250,7 +11243,7 @@
         <v>16</v>
       </c>
       <c r="B485" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C485" t="s">
         <v>8</v>
@@ -11267,7 +11260,7 @@
         <v>16</v>
       </c>
       <c r="B486" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C486" t="s">
         <v>8</v>
@@ -11284,7 +11277,7 @@
         <v>16</v>
       </c>
       <c r="B487" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C487" t="s">
         <v>8</v>
@@ -11318,7 +11311,7 @@
         <v>16</v>
       </c>
       <c r="B489" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C489" t="s">
         <v>8</v>
@@ -11335,7 +11328,7 @@
         <v>17</v>
       </c>
       <c r="B490" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C490" t="s">
         <v>8</v>
@@ -11352,7 +11345,7 @@
         <v>17</v>
       </c>
       <c r="B491" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C491" t="s">
         <v>8</v>
@@ -11369,7 +11362,7 @@
         <v>17</v>
       </c>
       <c r="B492" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C492" t="s">
         <v>8</v>
@@ -11420,7 +11413,7 @@
         <v>17</v>
       </c>
       <c r="B495" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C495" t="s">
         <v>8</v>
@@ -11437,7 +11430,7 @@
         <v>17</v>
       </c>
       <c r="B496" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C496" t="s">
         <v>8</v>
@@ -11454,7 +11447,7 @@
         <v>17</v>
       </c>
       <c r="B497" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C497" t="s">
         <v>8</v>
@@ -11488,7 +11481,7 @@
         <v>17</v>
       </c>
       <c r="B499" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C499" t="s">
         <v>8</v>
@@ -11505,7 +11498,7 @@
         <v>17</v>
       </c>
       <c r="B500" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C500" t="s">
         <v>8</v>
@@ -11522,7 +11515,7 @@
         <v>18</v>
       </c>
       <c r="B501" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C501" t="s">
         <v>8</v>
@@ -11539,7 +11532,7 @@
         <v>18</v>
       </c>
       <c r="B502" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C502" t="s">
         <v>8</v>
@@ -11556,7 +11549,7 @@
         <v>18</v>
       </c>
       <c r="B503" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C503" t="s">
         <v>8</v>
@@ -11573,7 +11566,7 @@
         <v>18</v>
       </c>
       <c r="B504" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C504" t="s">
         <v>8</v>
@@ -11675,7 +11668,7 @@
         <v>18</v>
       </c>
       <c r="B510" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C510" t="s">
         <v>8</v>
@@ -11692,7 +11685,7 @@
         <v>18</v>
       </c>
       <c r="B511" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C511" t="s">
         <v>8</v>
@@ -11709,7 +11702,7 @@
         <v>18</v>
       </c>
       <c r="B512" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C512" t="s">
         <v>8</v>
@@ -11726,7 +11719,7 @@
         <v>18</v>
       </c>
       <c r="B513" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C513" t="s">
         <v>8</v>
@@ -11760,7 +11753,7 @@
         <v>18</v>
       </c>
       <c r="B515" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C515" t="s">
         <v>8</v>
@@ -11777,7 +11770,7 @@
         <v>19</v>
       </c>
       <c r="B516" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C516" t="s">
         <v>8</v>
@@ -11794,7 +11787,7 @@
         <v>19</v>
       </c>
       <c r="B517" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C517" t="s">
         <v>8</v>
@@ -11811,7 +11804,7 @@
         <v>19</v>
       </c>
       <c r="B518" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C518" t="s">
         <v>8</v>
@@ -11828,7 +11821,7 @@
         <v>19</v>
       </c>
       <c r="B519" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C519" t="s">
         <v>8</v>
@@ -11845,7 +11838,7 @@
         <v>19</v>
       </c>
       <c r="B520" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C520" t="s">
         <v>8</v>
@@ -11862,7 +11855,7 @@
         <v>19</v>
       </c>
       <c r="B521" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C521" t="s">
         <v>8</v>
@@ -11879,7 +11872,7 @@
         <v>19</v>
       </c>
       <c r="B522" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C522" t="s">
         <v>8</v>
@@ -11896,7 +11889,7 @@
         <v>20</v>
       </c>
       <c r="B523" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C523" t="s">
         <v>8</v>
@@ -11913,7 +11906,7 @@
         <v>20</v>
       </c>
       <c r="B524" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C524" t="s">
         <v>8</v>
@@ -11930,7 +11923,7 @@
         <v>20</v>
       </c>
       <c r="B525" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C525" t="s">
         <v>8</v>
@@ -11947,7 +11940,7 @@
         <v>20</v>
       </c>
       <c r="B526" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C526" t="s">
         <v>8</v>
@@ -11964,7 +11957,7 @@
         <v>20</v>
       </c>
       <c r="B527" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C527" t="s">
         <v>8</v>
@@ -11981,7 +11974,7 @@
         <v>20</v>
       </c>
       <c r="B528" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C528" t="s">
         <v>8</v>
@@ -11998,7 +11991,7 @@
         <v>20</v>
       </c>
       <c r="B529" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C529" t="s">
         <v>8</v>
@@ -12015,7 +12008,7 @@
         <v>21</v>
       </c>
       <c r="B530" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C530" t="s">
         <v>8</v>
@@ -12032,7 +12025,7 @@
         <v>21</v>
       </c>
       <c r="B531" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C531" t="s">
         <v>8</v>
@@ -12049,7 +12042,7 @@
         <v>21</v>
       </c>
       <c r="B532" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C532" t="s">
         <v>8</v>
@@ -12066,7 +12059,7 @@
         <v>21</v>
       </c>
       <c r="B533" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C533" t="s">
         <v>8</v>
@@ -12083,7 +12076,7 @@
         <v>21</v>
       </c>
       <c r="B534" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C534" t="s">
         <v>8</v>
@@ -12100,7 +12093,7 @@
         <v>21</v>
       </c>
       <c r="B535" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C535" t="s">
         <v>8</v>
@@ -12117,7 +12110,7 @@
         <v>21</v>
       </c>
       <c r="B536" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C536" t="s">
         <v>8</v>
@@ -12134,7 +12127,7 @@
         <v>21</v>
       </c>
       <c r="B537" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C537" t="s">
         <v>8</v>
@@ -12151,7 +12144,7 @@
         <v>22</v>
       </c>
       <c r="B538" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C538" t="s">
         <v>8</v>
@@ -12253,7 +12246,7 @@
         <v>22</v>
       </c>
       <c r="B544" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C544" t="s">
         <v>8</v>
@@ -12270,7 +12263,7 @@
         <v>22</v>
       </c>
       <c r="B545" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C545" t="s">
         <v>8</v>
@@ -12338,7 +12331,7 @@
         <v>22</v>
       </c>
       <c r="B549" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C549" t="s">
         <v>8</v>
@@ -12355,7 +12348,7 @@
         <v>22</v>
       </c>
       <c r="B550" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C550" t="s">
         <v>8</v>
@@ -12372,7 +12365,7 @@
         <v>22</v>
       </c>
       <c r="B551" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C551" t="s">
         <v>8</v>
@@ -12389,7 +12382,7 @@
         <v>22</v>
       </c>
       <c r="B552" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C552" t="s">
         <v>8</v>
@@ -12406,7 +12399,7 @@
         <v>22</v>
       </c>
       <c r="B553" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C553" t="s">
         <v>8</v>
@@ -12423,7 +12416,7 @@
         <v>22</v>
       </c>
       <c r="B554" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C554" t="s">
         <v>8</v>
@@ -12474,7 +12467,7 @@
         <v>22</v>
       </c>
       <c r="B557" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C557" t="s">
         <v>8</v>
@@ -12491,7 +12484,7 @@
         <v>23</v>
       </c>
       <c r="B558" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C558" t="s">
         <v>8</v>
@@ -12508,7 +12501,7 @@
         <v>23</v>
       </c>
       <c r="B559" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C559" t="s">
         <v>8</v>
@@ -12525,7 +12518,7 @@
         <v>23</v>
       </c>
       <c r="B560" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C560" t="s">
         <v>8</v>
@@ -12542,7 +12535,7 @@
         <v>23</v>
       </c>
       <c r="B561" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C561" t="s">
         <v>8</v>
@@ -12576,7 +12569,7 @@
         <v>23</v>
       </c>
       <c r="B563" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C563" t="s">
         <v>8</v>
@@ -12593,7 +12586,7 @@
         <v>23</v>
       </c>
       <c r="B564" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C564" t="s">
         <v>8</v>
@@ -12627,7 +12620,7 @@
         <v>24</v>
       </c>
       <c r="B566" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C566" t="s">
         <v>8</v>
@@ -12644,7 +12637,7 @@
         <v>24</v>
       </c>
       <c r="B567" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C567" t="s">
         <v>8</v>
@@ -12661,7 +12654,7 @@
         <v>24</v>
       </c>
       <c r="B568" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C568" t="s">
         <v>8</v>
@@ -12678,7 +12671,7 @@
         <v>24</v>
       </c>
       <c r="B569" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C569" t="s">
         <v>8</v>
@@ -12695,7 +12688,7 @@
         <v>24</v>
       </c>
       <c r="B570" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C570" t="s">
         <v>8</v>
@@ -12712,7 +12705,7 @@
         <v>24</v>
       </c>
       <c r="B571" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C571" t="s">
         <v>8</v>
@@ -12729,7 +12722,7 @@
         <v>24</v>
       </c>
       <c r="B572" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C572" t="s">
         <v>8</v>
@@ -12763,7 +12756,7 @@
         <v>24</v>
       </c>
       <c r="B574" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C574" t="s">
         <v>8</v>
@@ -12780,7 +12773,7 @@
         <v>25</v>
       </c>
       <c r="B575" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C575" t="s">
         <v>8</v>
@@ -12797,7 +12790,7 @@
         <v>25</v>
       </c>
       <c r="B576" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C576" t="s">
         <v>8</v>
@@ -12814,7 +12807,7 @@
         <v>25</v>
       </c>
       <c r="B577" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C577" t="s">
         <v>8</v>
@@ -12831,7 +12824,7 @@
         <v>25</v>
       </c>
       <c r="B578" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C578" t="s">
         <v>8</v>
@@ -12848,7 +12841,7 @@
         <v>25</v>
       </c>
       <c r="B579" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C579" t="s">
         <v>8</v>
@@ -12882,7 +12875,7 @@
         <v>25</v>
       </c>
       <c r="B581" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C581" t="s">
         <v>8</v>
@@ -12899,7 +12892,7 @@
         <v>25</v>
       </c>
       <c r="B582" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C582" t="s">
         <v>8</v>
@@ -12933,7 +12926,7 @@
         <v>25</v>
       </c>
       <c r="B584" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C584" t="s">
         <v>8</v>
@@ -12950,7 +12943,7 @@
         <v>26</v>
       </c>
       <c r="B585" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C585" t="s">
         <v>8</v>
@@ -12967,7 +12960,7 @@
         <v>26</v>
       </c>
       <c r="B586" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C586" t="s">
         <v>8</v>
@@ -12984,7 +12977,7 @@
         <v>26</v>
       </c>
       <c r="B587" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C587" t="s">
         <v>8</v>
@@ -13001,7 +12994,7 @@
         <v>26</v>
       </c>
       <c r="B588" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C588" t="s">
         <v>8</v>
@@ -13018,7 +13011,7 @@
         <v>26</v>
       </c>
       <c r="B589" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C589" t="s">
         <v>8</v>
@@ -13035,7 +13028,7 @@
         <v>26</v>
       </c>
       <c r="B590" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C590" t="s">
         <v>8</v>
@@ -13052,7 +13045,7 @@
         <v>26</v>
       </c>
       <c r="B591" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C591" t="s">
         <v>8</v>
@@ -13086,7 +13079,7 @@
         <v>26</v>
       </c>
       <c r="B593" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C593" t="s">
         <v>8</v>
@@ -13103,7 +13096,7 @@
         <v>27</v>
       </c>
       <c r="B594" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C594" t="s">
         <v>8</v>
@@ -13120,7 +13113,7 @@
         <v>27</v>
       </c>
       <c r="B595" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C595" t="s">
         <v>8</v>
@@ -13137,7 +13130,7 @@
         <v>27</v>
       </c>
       <c r="B596" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C596" t="s">
         <v>8</v>
@@ -13154,7 +13147,7 @@
         <v>27</v>
       </c>
       <c r="B597" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C597" t="s">
         <v>8</v>
@@ -13307,7 +13300,7 @@
         <v>27</v>
       </c>
       <c r="B606" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C606" t="s">
         <v>8</v>
@@ -13324,7 +13317,7 @@
         <v>27</v>
       </c>
       <c r="B607" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C607" t="s">
         <v>8</v>
@@ -13358,7 +13351,7 @@
         <v>27</v>
       </c>
       <c r="B609" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C609" t="s">
         <v>8</v>
@@ -13392,7 +13385,7 @@
         <v>27</v>
       </c>
       <c r="B611" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C611" t="s">
         <v>8</v>
@@ -13409,7 +13402,7 @@
         <v>27</v>
       </c>
       <c r="B612" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C612" t="s">
         <v>8</v>
@@ -13426,7 +13419,7 @@
         <v>27</v>
       </c>
       <c r="B613" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C613" t="s">
         <v>8</v>
@@ -13443,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="B614" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C614" t="s">
         <v>8</v>
@@ -13477,7 +13470,7 @@
         <v>27</v>
       </c>
       <c r="B616" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C616" t="s">
         <v>8</v>
@@ -13529,12 +13522,12 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -13568,7 +13561,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -13908,7 +13901,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B24" t="s">
         <v>7</v>
@@ -13942,7 +13935,7 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B26" t="s">
         <v>7</v>
@@ -14293,7 +14286,7 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:I185"/>
+  <dimension ref="A1:H185"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -14301,20 +14294,19 @@
     <col min="3" max="4" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:8">
       <c r="A1" s="45" t="s">
         <v>87</v>
       </c>
       <c r="B1" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1" s="45" t="s">
         <v>212</v>
-      </c>
-      <c r="C1" s="45" t="s">
-        <v>213</v>
       </c>
       <c r="D1" s="45" t="s">
         <v>57</v>
@@ -14323,27 +14315,24 @@
         <v>4</v>
       </c>
       <c r="F1" s="45" t="s">
-        <v>214</v>
-      </c>
-      <c r="G1" s="46" t="s">
-        <v>91</v>
+        <v>213</v>
+      </c>
+      <c r="G1" s="45" t="s">
+        <v>209</v>
       </c>
       <c r="H1" s="45" t="s">
         <v>210</v>
       </c>
-      <c r="I1" s="45" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" t="s">
         <v>201</v>
-      </c>
-      <c r="C2" t="s">
-        <v>202</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -14355,24 +14344,21 @@
         <v>1200</v>
       </c>
       <c r="G2">
-        <v>8.7790000000000003E-3</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
         <v>0.01</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -14384,21 +14370,18 @@
         <v>1200</v>
       </c>
       <c r="G3">
-        <v>8.7790000000000003E-3</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
         <v>0.01</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
@@ -14413,16 +14396,13 @@
         <v>7500</v>
       </c>
       <c r="G4">
-        <v>2.134E-3</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
         <v>0.01</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -14430,7 +14410,7 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
@@ -14442,16 +14422,13 @@
         <v>7500</v>
       </c>
       <c r="G5">
-        <v>2.134E-3</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
         <v>0.01</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -14471,16 +14448,13 @@
         <v>1000</v>
       </c>
       <c r="G6">
-        <v>9.5930000000000008E-3</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -14500,16 +14474,13 @@
         <v>1000</v>
       </c>
       <c r="G7">
-        <v>9.5930000000000008E-3</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
         <v>0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -14529,16 +14500,13 @@
         <v>2800</v>
       </c>
       <c r="G8">
-        <v>4.0200000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
         <v>0.01</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -14558,16 +14526,13 @@
         <v>4300</v>
       </c>
       <c r="G9">
-        <v>2.6180000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
         <v>0.01</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -14587,16 +14552,13 @@
         <v>3400</v>
       </c>
       <c r="G10">
-        <v>4.6319999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10">
         <v>0.01</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -14616,16 +14578,13 @@
         <v>3400</v>
       </c>
       <c r="G11">
-        <v>4.6319999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11">
         <v>0.01</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -14645,16 +14604,13 @@
         <v>2400</v>
       </c>
       <c r="G12">
-        <v>8.4419999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12">
         <v>0.01</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -14674,21 +14630,18 @@
         <v>2400</v>
       </c>
       <c r="G13">
-        <v>8.4419999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13">
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C14" t="s">
         <v>9</v>
@@ -14703,16 +14656,13 @@
         <v>4200</v>
       </c>
       <c r="G14">
-        <v>5.7710000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14">
         <v>0.01</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -14720,7 +14670,7 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D15" t="s">
         <v>8</v>
@@ -14732,21 +14682,18 @@
         <v>4400</v>
       </c>
       <c r="G15">
-        <v>5.509E-3</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="I15">
         <v>0.01</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C16" t="s">
         <v>15</v>
@@ -14761,16 +14708,13 @@
         <v>2200</v>
       </c>
       <c r="G16">
-        <v>7.3699999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16">
         <v>0.01</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -14778,7 +14722,7 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D17" t="s">
         <v>8</v>
@@ -14790,16 +14734,13 @@
         <v>4500</v>
       </c>
       <c r="G17">
-        <v>3.6029999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="I17">
         <v>0.01</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -14819,16 +14760,13 @@
         <v>2200</v>
       </c>
       <c r="G18">
-        <v>5.143E-3</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="I18">
         <v>0.01</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -14848,16 +14786,13 @@
         <v>3000</v>
       </c>
       <c r="G19">
-        <v>3.7720000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19">
         <v>0.01</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -14877,16 +14812,13 @@
         <v>3500</v>
       </c>
       <c r="G20">
-        <v>4.2859999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>1</v>
-      </c>
-      <c r="I20">
         <v>0.01</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -14906,16 +14838,13 @@
         <v>3500</v>
       </c>
       <c r="G21">
-        <v>4.2859999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>1</v>
-      </c>
-      <c r="I21">
         <v>0.01</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -14935,16 +14864,13 @@
         <v>4800</v>
       </c>
       <c r="G22">
-        <v>4.2189999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="I22">
         <v>0.01</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -14964,16 +14890,13 @@
         <v>4800</v>
       </c>
       <c r="G23">
-        <v>4.2189999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>1</v>
-      </c>
-      <c r="I23">
         <v>0.01</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -14993,16 +14916,13 @@
         <v>5000</v>
       </c>
       <c r="G24">
-        <v>2.7590000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>1</v>
-      </c>
-      <c r="I24">
         <v>0.01</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -15022,16 +14942,13 @@
         <v>5000</v>
       </c>
       <c r="G25">
-        <v>2.7590000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>1</v>
-      </c>
-      <c r="I25">
         <v>0.01</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -15051,16 +14968,13 @@
         <v>1400</v>
       </c>
       <c r="G26">
-        <v>3.571E-3</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>1</v>
-      </c>
-      <c r="I26">
         <v>0.01</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:8">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -15080,16 +14994,13 @@
         <v>1400</v>
       </c>
       <c r="G27">
-        <v>3.571E-3</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>1</v>
-      </c>
-      <c r="I27">
         <v>0.01</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -15109,16 +15020,13 @@
         <v>2000</v>
       </c>
       <c r="G28">
-        <v>3.388E-3</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>1</v>
-      </c>
-      <c r="I28">
         <v>0.01</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:8">
       <c r="A29" t="s">
         <v>7</v>
       </c>
@@ -15138,16 +15046,13 @@
         <v>3000</v>
       </c>
       <c r="G29">
-        <v>2.2590000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>1</v>
-      </c>
-      <c r="I29">
         <v>0.01</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:8">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -15167,16 +15072,13 @@
         <v>1315</v>
       </c>
       <c r="G30">
-        <v>8.1300000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="I30">
         <v>0.01</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:8">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -15196,16 +15098,13 @@
         <v>1315</v>
       </c>
       <c r="G31">
-        <v>8.1300000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>1</v>
-      </c>
-      <c r="I31">
         <v>0.01</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:8">
       <c r="A32" t="s">
         <v>7</v>
       </c>
@@ -15225,16 +15124,13 @@
         <v>1400</v>
       </c>
       <c r="G32">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>1</v>
-      </c>
-      <c r="I32">
         <v>0.01</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:8">
       <c r="A33" t="s">
         <v>7</v>
       </c>
@@ -15254,16 +15150,13 @@
         <v>1400</v>
       </c>
       <c r="G33">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>1</v>
-      </c>
-      <c r="I33">
         <v>0.01</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:8">
       <c r="A34" t="s">
         <v>7</v>
       </c>
@@ -15283,16 +15176,13 @@
         <v>600</v>
       </c>
       <c r="G34">
-        <v>8.4030000000000007E-3</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>1</v>
-      </c>
-      <c r="I34">
         <v>0.01</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:8">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -15312,16 +15202,13 @@
         <v>590</v>
       </c>
       <c r="G35">
-        <v>8.5450000000000005E-3</v>
+        <v>1</v>
       </c>
       <c r="H35">
-        <v>1</v>
-      </c>
-      <c r="I35">
         <v>0.01</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:8">
       <c r="A36" t="s">
         <v>7</v>
       </c>
@@ -15341,16 +15228,13 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>1</v>
-      </c>
-      <c r="I36">
         <v>0.01</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:8">
       <c r="A37" t="s">
         <v>7</v>
       </c>
@@ -15370,16 +15254,13 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37">
-        <v>1</v>
-      </c>
-      <c r="I37">
         <v>0.01</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:8">
       <c r="A38" t="s">
         <v>7</v>
       </c>
@@ -15399,16 +15280,13 @@
         <v>1700</v>
       </c>
       <c r="G38">
-        <v>5.5469999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H38">
-        <v>1</v>
-      </c>
-      <c r="I38">
         <v>0.01</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:8">
       <c r="A39" t="s">
         <v>7</v>
       </c>
@@ -15428,16 +15306,13 @@
         <v>1300</v>
       </c>
       <c r="G39">
-        <v>7.254E-3</v>
+        <v>1</v>
       </c>
       <c r="H39">
-        <v>1</v>
-      </c>
-      <c r="I39">
         <v>0.01</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:8">
       <c r="A40" t="s">
         <v>7</v>
       </c>
@@ -15457,16 +15332,13 @@
         <v>700</v>
       </c>
       <c r="G40">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>1</v>
-      </c>
-      <c r="I40">
         <v>0.01</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:8">
       <c r="A41" t="s">
         <v>7</v>
       </c>
@@ -15486,16 +15358,13 @@
         <v>700</v>
       </c>
       <c r="G41">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>1</v>
-      </c>
-      <c r="I41">
         <v>0.01</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:8">
       <c r="A42" t="s">
         <v>7</v>
       </c>
@@ -15515,16 +15384,13 @@
         <v>1632</v>
       </c>
       <c r="G42">
-        <v>2.3080000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>1</v>
-      </c>
-      <c r="I42">
         <v>0.01</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:8">
       <c r="A43" t="s">
         <v>7</v>
       </c>
@@ -15544,16 +15410,13 @@
         <v>1632</v>
       </c>
       <c r="G43">
-        <v>2.3080000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H43">
-        <v>1</v>
-      </c>
-      <c r="I43">
         <v>0.01</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:8">
       <c r="A44" t="s">
         <v>7</v>
       </c>
@@ -15573,16 +15436,13 @@
         <v>715</v>
       </c>
       <c r="G44">
-        <v>6.8729999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>1</v>
-      </c>
-      <c r="I44">
         <v>0.01</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:8">
       <c r="A45" t="s">
         <v>7</v>
       </c>
@@ -15602,16 +15462,13 @@
         <v>715</v>
       </c>
       <c r="G45">
-        <v>6.8729999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H45">
-        <v>1</v>
-      </c>
-      <c r="I45">
         <v>0.01</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:8">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -15631,16 +15488,13 @@
         <v>1400</v>
       </c>
       <c r="G46">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H46">
-        <v>1</v>
-      </c>
-      <c r="I46">
         <v>0.01</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:8">
       <c r="A47" t="s">
         <v>7</v>
       </c>
@@ -15660,16 +15514,13 @@
         <v>1400</v>
       </c>
       <c r="G47">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>1</v>
-      </c>
-      <c r="I47">
         <v>0.01</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:8">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -15689,16 +15540,13 @@
         <v>1016</v>
       </c>
       <c r="G48">
-        <v>3.2859999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H48">
-        <v>1</v>
-      </c>
-      <c r="I48">
         <v>0.01</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:8">
       <c r="A49" t="s">
         <v>7</v>
       </c>
@@ -15718,16 +15566,13 @@
         <v>1016</v>
       </c>
       <c r="G49">
-        <v>3.2859999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>1</v>
-      </c>
-      <c r="I49">
         <v>0.01</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:8">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -15747,16 +15592,13 @@
         <v>950</v>
       </c>
       <c r="G50">
-        <v>3.3059999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>1</v>
-      </c>
-      <c r="I50">
         <v>0.01</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:8">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -15776,16 +15618,13 @@
         <v>879</v>
       </c>
       <c r="G51">
-        <v>3.5729999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>1</v>
-      </c>
-      <c r="I51">
         <v>0.01</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:8">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -15805,16 +15644,13 @@
         <v>5000</v>
       </c>
       <c r="G52">
-        <v>4.627E-3</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>1</v>
-      </c>
-      <c r="I52">
         <v>0.01</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:8">
       <c r="A53" t="s">
         <v>7</v>
       </c>
@@ -15834,16 +15670,13 @@
         <v>5000</v>
       </c>
       <c r="G53">
-        <v>4.627E-3</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>1</v>
-      </c>
-      <c r="I53">
         <v>0.01</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:8">
       <c r="A54" t="s">
         <v>7</v>
       </c>
@@ -15863,16 +15696,13 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54">
-        <v>1</v>
-      </c>
-      <c r="I54">
         <v>0.01</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:8">
       <c r="A55" t="s">
         <v>7</v>
       </c>
@@ -15892,16 +15722,13 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55">
-        <v>1</v>
-      </c>
-      <c r="I55">
         <v>0.01</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:8">
       <c r="A56" t="s">
         <v>7</v>
       </c>
@@ -15921,16 +15748,13 @@
         <v>2000</v>
       </c>
       <c r="G56">
-        <v>2.9039999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H56">
-        <v>1</v>
-      </c>
-      <c r="I56">
         <v>0.01</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:8">
       <c r="A57" t="s">
         <v>7</v>
       </c>
@@ -15950,16 +15774,13 @@
         <v>2000</v>
       </c>
       <c r="G57">
-        <v>2.9039999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H57">
-        <v>1</v>
-      </c>
-      <c r="I57">
         <v>0.01</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:8">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -15979,16 +15800,13 @@
         <v>1200</v>
       </c>
       <c r="G58">
-        <v>4.1539999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H58">
-        <v>1</v>
-      </c>
-      <c r="I58">
         <v>0.01</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:8">
       <c r="A59" t="s">
         <v>7</v>
       </c>
@@ -16008,16 +15826,13 @@
         <v>1200</v>
       </c>
       <c r="G59">
-        <v>4.1539999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>1</v>
-      </c>
-      <c r="I59">
         <v>0.01</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:8">
       <c r="A60" t="s">
         <v>7</v>
       </c>
@@ -16037,16 +15852,13 @@
         <v>5600</v>
       </c>
       <c r="G60">
-        <v>4.3889999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H60">
-        <v>1</v>
-      </c>
-      <c r="I60">
         <v>0.01</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:8">
       <c r="A61" t="s">
         <v>7</v>
       </c>
@@ -16066,16 +15878,13 @@
         <v>5600</v>
       </c>
       <c r="G61">
-        <v>4.3889999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H61">
-        <v>1</v>
-      </c>
-      <c r="I61">
         <v>0.01</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:8">
       <c r="A62" t="s">
         <v>7</v>
       </c>
@@ -16095,16 +15904,13 @@
         <v>950</v>
       </c>
       <c r="G62">
-        <v>3.3210000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H62">
-        <v>1</v>
-      </c>
-      <c r="I62">
         <v>0.01</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:8">
       <c r="A63" t="s">
         <v>7</v>
       </c>
@@ -16124,16 +15930,13 @@
         <v>950</v>
       </c>
       <c r="G63">
-        <v>3.3210000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H63">
-        <v>1</v>
-      </c>
-      <c r="I63">
         <v>0.01</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:8">
       <c r="A64" t="s">
         <v>7</v>
       </c>
@@ -16153,16 +15956,13 @@
         <v>700</v>
       </c>
       <c r="G64">
-        <v>8.796E-3</v>
+        <v>1</v>
       </c>
       <c r="H64">
-        <v>1</v>
-      </c>
-      <c r="I64">
         <v>0.01</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:8">
       <c r="A65" t="s">
         <v>7</v>
       </c>
@@ -16182,16 +15982,13 @@
         <v>700</v>
       </c>
       <c r="G65">
-        <v>8.796E-3</v>
+        <v>1</v>
       </c>
       <c r="H65">
-        <v>1</v>
-      </c>
-      <c r="I65">
         <v>0.01</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:8">
       <c r="A66" t="s">
         <v>7</v>
       </c>
@@ -16211,16 +16008,13 @@
         <v>700</v>
       </c>
       <c r="G66">
-        <v>4.8089999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H66">
-        <v>1</v>
-      </c>
-      <c r="I66">
         <v>0.01</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:8">
       <c r="A67" t="s">
         <v>7</v>
       </c>
@@ -16240,16 +16034,13 @@
         <v>700</v>
       </c>
       <c r="G67">
-        <v>4.8089999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>1</v>
-      </c>
-      <c r="I67">
         <v>0.01</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:8">
       <c r="A68" t="s">
         <v>7</v>
       </c>
@@ -16269,16 +16060,13 @@
         <v>700</v>
       </c>
       <c r="G68">
-        <v>3.813E-3</v>
+        <v>1</v>
       </c>
       <c r="H68">
-        <v>1</v>
-      </c>
-      <c r="I68">
         <v>0.01</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:8">
       <c r="A69" t="s">
         <v>7</v>
       </c>
@@ -16298,16 +16086,13 @@
         <v>700</v>
       </c>
       <c r="G69">
-        <v>3.813E-3</v>
+        <v>1</v>
       </c>
       <c r="H69">
-        <v>1</v>
-      </c>
-      <c r="I69">
         <v>0.01</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:8">
       <c r="A70" t="s">
         <v>7</v>
       </c>
@@ -16327,16 +16112,13 @@
         <v>2800</v>
       </c>
       <c r="G70">
-        <v>9.7680000000000006E-3</v>
+        <v>1</v>
       </c>
       <c r="H70">
-        <v>1</v>
-      </c>
-      <c r="I70">
         <v>0.01</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:8">
       <c r="A71" t="s">
         <v>7</v>
       </c>
@@ -16356,16 +16138,13 @@
         <v>2800</v>
       </c>
       <c r="G71">
-        <v>9.7680000000000006E-3</v>
+        <v>1</v>
       </c>
       <c r="H71">
-        <v>1</v>
-      </c>
-      <c r="I71">
         <v>0.01</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:8">
       <c r="A72" t="s">
         <v>7</v>
       </c>
@@ -16385,16 +16164,13 @@
         <v>350</v>
       </c>
       <c r="G72">
-        <v>2.5279999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H72">
-        <v>1</v>
-      </c>
-      <c r="I72">
         <v>0.01</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:8">
       <c r="A73" t="s">
         <v>7</v>
       </c>
@@ -16414,16 +16190,13 @@
         <v>1300</v>
       </c>
       <c r="G73">
-        <v>6.8099999999999996E-4</v>
+        <v>1</v>
       </c>
       <c r="H73">
-        <v>1</v>
-      </c>
-      <c r="I73">
         <v>0.01</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:8">
       <c r="A74" t="s">
         <v>7</v>
       </c>
@@ -16443,16 +16216,13 @@
         <v>800</v>
       </c>
       <c r="G74">
-        <v>1.603E-3</v>
+        <v>1</v>
       </c>
       <c r="H74">
-        <v>1</v>
-      </c>
-      <c r="I74">
         <v>0.01</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:8">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -16472,16 +16242,13 @@
         <v>600</v>
       </c>
       <c r="G75">
-        <v>2.137E-3</v>
+        <v>1</v>
       </c>
       <c r="H75">
-        <v>1</v>
-      </c>
-      <c r="I75">
         <v>0.01</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:8">
       <c r="A76" t="s">
         <v>7</v>
       </c>
@@ -16501,16 +16268,13 @@
         <v>600</v>
       </c>
       <c r="G76">
-        <v>3.9880000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H76">
-        <v>1</v>
-      </c>
-      <c r="I76">
         <v>0.01</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:8">
       <c r="A77" t="s">
         <v>7</v>
       </c>
@@ -16530,16 +16294,13 @@
         <v>1000</v>
       </c>
       <c r="G77">
-        <v>2.3930000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H77">
-        <v>1</v>
-      </c>
-      <c r="I77">
         <v>0.01</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:8">
       <c r="A78" t="s">
         <v>7</v>
       </c>
@@ -16559,16 +16320,13 @@
         <v>700</v>
       </c>
       <c r="G78">
-        <v>4.3309999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H78">
-        <v>1</v>
-      </c>
-      <c r="I78">
         <v>0.01</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:8">
       <c r="A79" t="s">
         <v>7</v>
       </c>
@@ -16588,16 +16346,13 @@
         <v>600</v>
       </c>
       <c r="G79">
-        <v>5.0530000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H79">
-        <v>1</v>
-      </c>
-      <c r="I79">
         <v>0.01</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:8">
       <c r="A80" t="s">
         <v>7</v>
       </c>
@@ -16617,16 +16372,13 @@
         <v>250</v>
       </c>
       <c r="G80">
-        <v>3.2550000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H80">
-        <v>1</v>
-      </c>
-      <c r="I80">
         <v>0.01</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:8">
       <c r="A81" t="s">
         <v>7</v>
       </c>
@@ -16646,16 +16398,13 @@
         <v>300</v>
       </c>
       <c r="G81">
-        <v>2.7130000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H81">
-        <v>1</v>
-      </c>
-      <c r="I81">
         <v>0.01</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:8">
       <c r="A82" t="s">
         <v>7</v>
       </c>
@@ -16675,16 +16424,13 @@
         <v>2145</v>
       </c>
       <c r="G82">
-        <v>4.248E-3</v>
+        <v>1</v>
       </c>
       <c r="H82">
-        <v>1</v>
-      </c>
-      <c r="I82">
         <v>0.01</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:8">
       <c r="A83" t="s">
         <v>7</v>
       </c>
@@ -16704,16 +16450,13 @@
         <v>2095</v>
       </c>
       <c r="G83">
-        <v>4.3489999999999996E-3</v>
+        <v>1</v>
       </c>
       <c r="H83">
-        <v>1</v>
-      </c>
-      <c r="I83">
         <v>0.01</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:8">
       <c r="A84" t="s">
         <v>7</v>
       </c>
@@ -16733,16 +16476,13 @@
         <v>1400</v>
       </c>
       <c r="G84">
-        <v>2.7680000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H84">
-        <v>1</v>
-      </c>
-      <c r="I84">
         <v>0.01</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:8">
       <c r="A85" t="s">
         <v>7</v>
       </c>
@@ -16762,16 +16502,13 @@
         <v>1400</v>
       </c>
       <c r="G85">
-        <v>2.7680000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H85">
-        <v>1</v>
-      </c>
-      <c r="I85">
         <v>0.01</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:8">
       <c r="A86" t="s">
         <v>7</v>
       </c>
@@ -16791,16 +16528,13 @@
         <v>600</v>
       </c>
       <c r="G86">
-        <v>8.3330000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H86">
-        <v>1</v>
-      </c>
-      <c r="I86">
         <v>0.01</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:8">
       <c r="A87" t="s">
         <v>7</v>
       </c>
@@ -16820,16 +16554,13 @@
         <v>600</v>
       </c>
       <c r="G87">
-        <v>8.3330000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H87">
-        <v>1</v>
-      </c>
-      <c r="I87">
         <v>0.01</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:8">
       <c r="A88" t="s">
         <v>7</v>
       </c>
@@ -16849,16 +16580,13 @@
         <v>3300</v>
       </c>
       <c r="G88">
-        <v>2.1359999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H88">
-        <v>1</v>
-      </c>
-      <c r="I88">
         <v>0.01</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:8">
       <c r="A89" t="s">
         <v>7</v>
       </c>
@@ -16878,16 +16606,13 @@
         <v>3300</v>
       </c>
       <c r="G89">
-        <v>2.1359999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H89">
-        <v>1</v>
-      </c>
-      <c r="I89">
         <v>0.01</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:8">
       <c r="A90" t="s">
         <v>7</v>
       </c>
@@ -16907,16 +16632,13 @@
         <v>7300</v>
       </c>
       <c r="G90">
-        <v>1.8680000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H90">
-        <v>1</v>
-      </c>
-      <c r="I90">
         <v>0.01</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:8">
       <c r="A91" t="s">
         <v>7</v>
       </c>
@@ -16936,16 +16658,13 @@
         <v>7300</v>
       </c>
       <c r="G91">
-        <v>1.8680000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H91">
-        <v>1</v>
-      </c>
-      <c r="I91">
         <v>0.01</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:8">
       <c r="A92" t="s">
         <v>7</v>
       </c>
@@ -16965,16 +16684,13 @@
         <v>6200</v>
       </c>
       <c r="G92">
-        <v>2.679E-3</v>
+        <v>1</v>
       </c>
       <c r="H92">
-        <v>1</v>
-      </c>
-      <c r="I92">
         <v>0.01</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:8">
       <c r="A93" t="s">
         <v>7</v>
       </c>
@@ -16994,24 +16710,21 @@
         <v>2800</v>
       </c>
       <c r="G93">
-        <v>5.9319999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H93">
-        <v>1</v>
-      </c>
-      <c r="I93">
         <v>0.01</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:8">
       <c r="A94" t="s">
         <v>7</v>
       </c>
       <c r="B94" t="s">
+        <v>200</v>
+      </c>
+      <c r="C94" t="s">
         <v>201</v>
-      </c>
-      <c r="C94" t="s">
-        <v>202</v>
       </c>
       <c r="D94" t="s">
         <v>8</v>
@@ -17023,24 +16736,21 @@
         <v>1200</v>
       </c>
       <c r="G94">
-        <v>8.7790000000000003E-3</v>
+        <v>1</v>
       </c>
       <c r="H94">
-        <v>1</v>
-      </c>
-      <c r="I94">
         <v>0.01</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:8">
       <c r="A95" t="s">
         <v>7</v>
       </c>
       <c r="B95" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C95" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D95" t="s">
         <v>8</v>
@@ -17052,21 +16762,18 @@
         <v>1200</v>
       </c>
       <c r="G95">
-        <v>8.7790000000000003E-3</v>
+        <v>1</v>
       </c>
       <c r="H95">
-        <v>1</v>
-      </c>
-      <c r="I95">
         <v>0.01</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:8">
       <c r="A96" t="s">
         <v>7</v>
       </c>
       <c r="B96" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C96" t="s">
         <v>9</v>
@@ -17081,16 +16788,13 @@
         <v>7500</v>
       </c>
       <c r="G96">
-        <v>2.134E-3</v>
+        <v>1</v>
       </c>
       <c r="H96">
-        <v>1</v>
-      </c>
-      <c r="I96">
         <v>0.01</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:8">
       <c r="A97" t="s">
         <v>7</v>
       </c>
@@ -17098,7 +16802,7 @@
         <v>9</v>
       </c>
       <c r="C97" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D97" t="s">
         <v>8</v>
@@ -17110,16 +16814,13 @@
         <v>7500</v>
       </c>
       <c r="G97">
-        <v>2.134E-3</v>
+        <v>1</v>
       </c>
       <c r="H97">
-        <v>1</v>
-      </c>
-      <c r="I97">
         <v>0.01</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:8">
       <c r="A98" t="s">
         <v>7</v>
       </c>
@@ -17139,16 +16840,13 @@
         <v>1000</v>
       </c>
       <c r="G98">
-        <v>9.5930000000000008E-3</v>
+        <v>1</v>
       </c>
       <c r="H98">
-        <v>1</v>
-      </c>
-      <c r="I98">
         <v>0.01</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:8">
       <c r="A99" t="s">
         <v>7</v>
       </c>
@@ -17168,16 +16866,13 @@
         <v>1000</v>
       </c>
       <c r="G99">
-        <v>9.5930000000000008E-3</v>
+        <v>1</v>
       </c>
       <c r="H99">
-        <v>1</v>
-      </c>
-      <c r="I99">
         <v>0.01</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:8">
       <c r="A100" t="s">
         <v>7</v>
       </c>
@@ -17197,16 +16892,13 @@
         <v>3800</v>
       </c>
       <c r="G100">
-        <v>4.0200000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H100">
-        <v>1</v>
-      </c>
-      <c r="I100">
         <v>0.01</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:8">
       <c r="A101" t="s">
         <v>7</v>
       </c>
@@ -17226,16 +16918,13 @@
         <v>5300</v>
       </c>
       <c r="G101">
-        <v>2.882E-3</v>
+        <v>1</v>
       </c>
       <c r="H101">
-        <v>1</v>
-      </c>
-      <c r="I101">
         <v>0.01</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:8">
       <c r="A102" t="s">
         <v>7</v>
       </c>
@@ -17255,16 +16944,13 @@
         <v>5400</v>
       </c>
       <c r="G102">
-        <v>4.6319999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H102">
-        <v>1</v>
-      </c>
-      <c r="I102">
         <v>0.01</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:8">
       <c r="A103" t="s">
         <v>7</v>
       </c>
@@ -17284,16 +16970,13 @@
         <v>4400</v>
       </c>
       <c r="G103">
-        <v>5.6849999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H103">
-        <v>1</v>
-      </c>
-      <c r="I103">
         <v>0.01</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:8">
       <c r="A104" t="s">
         <v>7</v>
       </c>
@@ -17313,16 +16996,13 @@
         <v>4800</v>
       </c>
       <c r="G104">
-        <v>8.4419999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H104">
-        <v>1</v>
-      </c>
-      <c r="I104">
         <v>0.01</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:8">
       <c r="A105" t="s">
         <v>7</v>
       </c>
@@ -17342,21 +17022,18 @@
         <v>4800</v>
       </c>
       <c r="G105">
-        <v>8.4419999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H105">
-        <v>1</v>
-      </c>
-      <c r="I105">
         <v>0.01</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:8">
       <c r="A106" t="s">
         <v>7</v>
       </c>
       <c r="B106" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C106" t="s">
         <v>9</v>
@@ -17371,16 +17048,13 @@
         <v>4500</v>
       </c>
       <c r="G106">
-        <v>5.7710000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H106">
-        <v>1</v>
-      </c>
-      <c r="I106">
         <v>0.01</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:8">
       <c r="A107" t="s">
         <v>7</v>
       </c>
@@ -17388,7 +17062,7 @@
         <v>9</v>
       </c>
       <c r="C107" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D107" t="s">
         <v>8</v>
@@ -17400,21 +17074,18 @@
         <v>5000</v>
       </c>
       <c r="G107">
-        <v>5.1939999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H107">
-        <v>1</v>
-      </c>
-      <c r="I107">
         <v>0.01</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:8">
       <c r="A108" t="s">
         <v>7</v>
       </c>
       <c r="B108" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C108" t="s">
         <v>15</v>
@@ -17429,16 +17100,13 @@
         <v>2200</v>
       </c>
       <c r="G108">
-        <v>7.3699999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H108">
-        <v>1</v>
-      </c>
-      <c r="I108">
         <v>0.01</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:8">
       <c r="A109" t="s">
         <v>7</v>
       </c>
@@ -17446,7 +17114,7 @@
         <v>15</v>
       </c>
       <c r="C109" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D109" t="s">
         <v>8</v>
@@ -17458,16 +17126,13 @@
         <v>4500</v>
       </c>
       <c r="G109">
-        <v>3.6029999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H109">
-        <v>1</v>
-      </c>
-      <c r="I109">
         <v>0.01</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:8">
       <c r="A110" t="s">
         <v>7</v>
       </c>
@@ -17487,16 +17152,13 @@
         <v>2200</v>
       </c>
       <c r="G110">
-        <v>5.143E-3</v>
+        <v>1</v>
       </c>
       <c r="H110">
-        <v>1</v>
-      </c>
-      <c r="I110">
         <v>0.01</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:8">
       <c r="A111" t="s">
         <v>7</v>
       </c>
@@ -17516,16 +17178,13 @@
         <v>3000</v>
       </c>
       <c r="G111">
-        <v>3.7720000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H111">
-        <v>1</v>
-      </c>
-      <c r="I111">
         <v>0.01</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:8">
       <c r="A112" t="s">
         <v>7</v>
       </c>
@@ -17545,16 +17204,13 @@
         <v>3500</v>
       </c>
       <c r="G112">
-        <v>4.2859999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H112">
-        <v>1</v>
-      </c>
-      <c r="I112">
         <v>0.01</v>
       </c>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:8">
       <c r="A113" t="s">
         <v>7</v>
       </c>
@@ -17574,16 +17230,13 @@
         <v>3500</v>
       </c>
       <c r="G113">
-        <v>4.2859999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H113">
-        <v>1</v>
-      </c>
-      <c r="I113">
         <v>0.01</v>
       </c>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:8">
       <c r="A114" t="s">
         <v>7</v>
       </c>
@@ -17603,16 +17256,13 @@
         <v>4800</v>
       </c>
       <c r="G114">
-        <v>4.2189999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H114">
-        <v>1</v>
-      </c>
-      <c r="I114">
         <v>0.01</v>
       </c>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:8">
       <c r="A115" t="s">
         <v>7</v>
       </c>
@@ -17632,16 +17282,13 @@
         <v>4800</v>
       </c>
       <c r="G115">
-        <v>4.2189999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H115">
-        <v>1</v>
-      </c>
-      <c r="I115">
         <v>0.01</v>
       </c>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:8">
       <c r="A116" t="s">
         <v>7</v>
       </c>
@@ -17661,16 +17308,13 @@
         <v>5000</v>
       </c>
       <c r="G116">
-        <v>2.7590000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H116">
-        <v>1</v>
-      </c>
-      <c r="I116">
         <v>0.01</v>
       </c>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:8">
       <c r="A117" t="s">
         <v>7</v>
       </c>
@@ -17690,16 +17334,13 @@
         <v>5000</v>
       </c>
       <c r="G117">
-        <v>2.7590000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H117">
-        <v>1</v>
-      </c>
-      <c r="I117">
         <v>0.01</v>
       </c>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:8">
       <c r="A118" t="s">
         <v>7</v>
       </c>
@@ -17719,16 +17360,13 @@
         <v>1400</v>
       </c>
       <c r="G118">
-        <v>3.571E-3</v>
+        <v>1</v>
       </c>
       <c r="H118">
-        <v>1</v>
-      </c>
-      <c r="I118">
         <v>0.01</v>
       </c>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:8">
       <c r="A119" t="s">
         <v>7</v>
       </c>
@@ -17748,16 +17386,13 @@
         <v>1400</v>
       </c>
       <c r="G119">
-        <v>3.571E-3</v>
+        <v>1</v>
       </c>
       <c r="H119">
-        <v>1</v>
-      </c>
-      <c r="I119">
         <v>0.01</v>
       </c>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:8">
       <c r="A120" t="s">
         <v>7</v>
       </c>
@@ -17777,16 +17412,13 @@
         <v>2000</v>
       </c>
       <c r="G120">
-        <v>3.388E-3</v>
+        <v>1</v>
       </c>
       <c r="H120">
-        <v>1</v>
-      </c>
-      <c r="I120">
         <v>0.01</v>
       </c>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:8">
       <c r="A121" t="s">
         <v>7</v>
       </c>
@@ -17806,16 +17438,13 @@
         <v>3000</v>
       </c>
       <c r="G121">
-        <v>2.2590000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H121">
-        <v>1</v>
-      </c>
-      <c r="I121">
         <v>0.01</v>
       </c>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:8">
       <c r="A122" t="s">
         <v>7</v>
       </c>
@@ -17835,16 +17464,13 @@
         <v>2015</v>
       </c>
       <c r="G122">
-        <v>8.1300000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H122">
-        <v>1</v>
-      </c>
-      <c r="I122">
         <v>0.01</v>
       </c>
     </row>
-    <row r="123" spans="1:9">
+    <row r="123" spans="1:8">
       <c r="A123" t="s">
         <v>7</v>
       </c>
@@ -17864,16 +17490,13 @@
         <v>2015</v>
       </c>
       <c r="G123">
-        <v>8.1300000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H123">
-        <v>1</v>
-      </c>
-      <c r="I123">
         <v>0.01</v>
       </c>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" spans="1:8">
       <c r="A124" t="s">
         <v>7</v>
       </c>
@@ -17893,16 +17516,13 @@
         <v>2800</v>
       </c>
       <c r="G124">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H124">
-        <v>1</v>
-      </c>
-      <c r="I124">
         <v>0.01</v>
       </c>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:8">
       <c r="A125" t="s">
         <v>7</v>
       </c>
@@ -17922,16 +17542,13 @@
         <v>2800</v>
       </c>
       <c r="G125">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H125">
-        <v>1</v>
-      </c>
-      <c r="I125">
         <v>0.01</v>
       </c>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" spans="1:8">
       <c r="A126" t="s">
         <v>7</v>
       </c>
@@ -17951,16 +17568,13 @@
         <v>600</v>
       </c>
       <c r="G126">
-        <v>8.4030000000000007E-3</v>
+        <v>1</v>
       </c>
       <c r="H126">
-        <v>1</v>
-      </c>
-      <c r="I126">
         <v>0.01</v>
       </c>
     </row>
-    <row r="127" spans="1:9">
+    <row r="127" spans="1:8">
       <c r="A127" t="s">
         <v>7</v>
       </c>
@@ -17980,16 +17594,13 @@
         <v>590</v>
       </c>
       <c r="G127">
-        <v>8.5450000000000005E-3</v>
+        <v>1</v>
       </c>
       <c r="H127">
-        <v>1</v>
-      </c>
-      <c r="I127">
         <v>0.01</v>
       </c>
     </row>
-    <row r="128" spans="1:9">
+    <row r="128" spans="1:8">
       <c r="A128" t="s">
         <v>7</v>
       </c>
@@ -18009,16 +17620,13 @@
         <v>0</v>
       </c>
       <c r="G128">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H128">
-        <v>1</v>
-      </c>
-      <c r="I128">
         <v>0.01</v>
       </c>
     </row>
-    <row r="129" spans="1:9">
+    <row r="129" spans="1:8">
       <c r="A129" t="s">
         <v>7</v>
       </c>
@@ -18038,16 +17646,13 @@
         <v>0</v>
       </c>
       <c r="G129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H129">
-        <v>1</v>
-      </c>
-      <c r="I129">
         <v>0.01</v>
       </c>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:8">
       <c r="A130" t="s">
         <v>7</v>
       </c>
@@ -18067,16 +17672,13 @@
         <v>1700</v>
       </c>
       <c r="G130">
-        <v>5.5469999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H130">
-        <v>1</v>
-      </c>
-      <c r="I130">
         <v>0.01</v>
       </c>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" spans="1:8">
       <c r="A131" t="s">
         <v>7</v>
       </c>
@@ -18096,16 +17698,13 @@
         <v>1300</v>
       </c>
       <c r="G131">
-        <v>7.254E-3</v>
+        <v>1</v>
       </c>
       <c r="H131">
-        <v>1</v>
-      </c>
-      <c r="I131">
         <v>0.01</v>
       </c>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:8">
       <c r="A132" t="s">
         <v>7</v>
       </c>
@@ -18125,16 +17724,13 @@
         <v>700</v>
       </c>
       <c r="G132">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H132">
-        <v>1</v>
-      </c>
-      <c r="I132">
         <v>0.01</v>
       </c>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" spans="1:8">
       <c r="A133" t="s">
         <v>7</v>
       </c>
@@ -18154,16 +17750,13 @@
         <v>700</v>
       </c>
       <c r="G133">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H133">
-        <v>1</v>
-      </c>
-      <c r="I133">
         <v>0.01</v>
       </c>
     </row>
-    <row r="134" spans="1:9">
+    <row r="134" spans="1:8">
       <c r="A134" t="s">
         <v>7</v>
       </c>
@@ -18183,16 +17776,13 @@
         <v>1632</v>
       </c>
       <c r="G134">
-        <v>2.3080000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H134">
-        <v>1</v>
-      </c>
-      <c r="I134">
         <v>0.01</v>
       </c>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" spans="1:8">
       <c r="A135" t="s">
         <v>7</v>
       </c>
@@ -18212,16 +17802,13 @@
         <v>1632</v>
       </c>
       <c r="G135">
-        <v>2.3080000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H135">
-        <v>1</v>
-      </c>
-      <c r="I135">
         <v>0.01</v>
       </c>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:8">
       <c r="A136" t="s">
         <v>7</v>
       </c>
@@ -18241,16 +17828,13 @@
         <v>715</v>
       </c>
       <c r="G136">
-        <v>6.8729999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H136">
-        <v>1</v>
-      </c>
-      <c r="I136">
         <v>0.01</v>
       </c>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:8">
       <c r="A137" t="s">
         <v>7</v>
       </c>
@@ -18270,16 +17854,13 @@
         <v>715</v>
       </c>
       <c r="G137">
-        <v>6.8729999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H137">
-        <v>1</v>
-      </c>
-      <c r="I137">
         <v>0.01</v>
       </c>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:8">
       <c r="A138" t="s">
         <v>7</v>
       </c>
@@ -18299,16 +17880,13 @@
         <v>2800</v>
       </c>
       <c r="G138">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H138">
-        <v>1</v>
-      </c>
-      <c r="I138">
         <v>0.01</v>
       </c>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" spans="1:8">
       <c r="A139" t="s">
         <v>7</v>
       </c>
@@ -18328,16 +17906,13 @@
         <v>2800</v>
       </c>
       <c r="G139">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H139">
-        <v>1</v>
-      </c>
-      <c r="I139">
         <v>0.01</v>
       </c>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" spans="1:8">
       <c r="A140" t="s">
         <v>7</v>
       </c>
@@ -18357,16 +17932,13 @@
         <v>1716</v>
       </c>
       <c r="G140">
-        <v>3.2859999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H140">
-        <v>1</v>
-      </c>
-      <c r="I140">
         <v>0.01</v>
       </c>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" spans="1:8">
       <c r="A141" t="s">
         <v>7</v>
       </c>
@@ -18386,16 +17958,13 @@
         <v>1716</v>
       </c>
       <c r="G141">
-        <v>3.2859999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H141">
-        <v>1</v>
-      </c>
-      <c r="I141">
         <v>0.01</v>
       </c>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:8">
       <c r="A142" t="s">
         <v>7</v>
       </c>
@@ -18415,16 +17984,13 @@
         <v>1950</v>
       </c>
       <c r="G142">
-        <v>3.3059999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H142">
-        <v>1</v>
-      </c>
-      <c r="I142">
         <v>0.01</v>
       </c>
     </row>
-    <row r="143" spans="1:9">
+    <row r="143" spans="1:8">
       <c r="A143" t="s">
         <v>7</v>
       </c>
@@ -18444,16 +18010,13 @@
         <v>1879</v>
       </c>
       <c r="G143">
-        <v>3.431E-3</v>
+        <v>1</v>
       </c>
       <c r="H143">
-        <v>1</v>
-      </c>
-      <c r="I143">
         <v>0.01</v>
       </c>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:8">
       <c r="A144" t="s">
         <v>7</v>
       </c>
@@ -18473,16 +18036,13 @@
         <v>6500</v>
       </c>
       <c r="G144">
-        <v>4.627E-3</v>
+        <v>1</v>
       </c>
       <c r="H144">
-        <v>1</v>
-      </c>
-      <c r="I144">
         <v>0.01</v>
       </c>
     </row>
-    <row r="145" spans="1:9">
+    <row r="145" spans="1:8">
       <c r="A145" t="s">
         <v>7</v>
       </c>
@@ -18502,16 +18062,13 @@
         <v>6500</v>
       </c>
       <c r="G145">
-        <v>4.627E-3</v>
+        <v>1</v>
       </c>
       <c r="H145">
-        <v>1</v>
-      </c>
-      <c r="I145">
         <v>0.01</v>
       </c>
     </row>
-    <row r="146" spans="1:9">
+    <row r="146" spans="1:8">
       <c r="A146" t="s">
         <v>7</v>
       </c>
@@ -18531,16 +18088,13 @@
         <v>0</v>
       </c>
       <c r="G146">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H146">
-        <v>1</v>
-      </c>
-      <c r="I146">
         <v>0.01</v>
       </c>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:8">
       <c r="A147" t="s">
         <v>7</v>
       </c>
@@ -18560,16 +18114,13 @@
         <v>0</v>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H147">
-        <v>1</v>
-      </c>
-      <c r="I147">
         <v>0.01</v>
       </c>
     </row>
-    <row r="148" spans="1:9">
+    <row r="148" spans="1:8">
       <c r="A148" t="s">
         <v>7</v>
       </c>
@@ -18589,16 +18140,13 @@
         <v>2800</v>
       </c>
       <c r="G148">
-        <v>2.9039999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H148">
-        <v>1</v>
-      </c>
-      <c r="I148">
         <v>0.01</v>
       </c>
     </row>
-    <row r="149" spans="1:9">
+    <row r="149" spans="1:8">
       <c r="A149" t="s">
         <v>7</v>
       </c>
@@ -18618,16 +18166,13 @@
         <v>2800</v>
       </c>
       <c r="G149">
-        <v>2.9039999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H149">
-        <v>1</v>
-      </c>
-      <c r="I149">
         <v>0.01</v>
       </c>
     </row>
-    <row r="150" spans="1:9">
+    <row r="150" spans="1:8">
       <c r="A150" t="s">
         <v>7</v>
       </c>
@@ -18647,16 +18192,13 @@
         <v>1200</v>
       </c>
       <c r="G150">
-        <v>4.1539999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H150">
-        <v>1</v>
-      </c>
-      <c r="I150">
         <v>0.01</v>
       </c>
     </row>
-    <row r="151" spans="1:9">
+    <row r="151" spans="1:8">
       <c r="A151" t="s">
         <v>7</v>
       </c>
@@ -18676,16 +18218,13 @@
         <v>1200</v>
       </c>
       <c r="G151">
-        <v>4.1539999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H151">
-        <v>1</v>
-      </c>
-      <c r="I151">
         <v>0.01</v>
       </c>
     </row>
-    <row r="152" spans="1:9">
+    <row r="152" spans="1:8">
       <c r="A152" t="s">
         <v>7</v>
       </c>
@@ -18705,16 +18244,13 @@
         <v>8725</v>
       </c>
       <c r="G152">
-        <v>4.3889999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H152">
-        <v>1</v>
-      </c>
-      <c r="I152">
         <v>0.01</v>
       </c>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:8">
       <c r="A153" t="s">
         <v>7</v>
       </c>
@@ -18734,16 +18270,13 @@
         <v>8725</v>
       </c>
       <c r="G153">
-        <v>4.3889999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H153">
-        <v>1</v>
-      </c>
-      <c r="I153">
         <v>0.01</v>
       </c>
     </row>
-    <row r="154" spans="1:9">
+    <row r="154" spans="1:8">
       <c r="A154" t="s">
         <v>7</v>
       </c>
@@ -18763,16 +18296,13 @@
         <v>950</v>
       </c>
       <c r="G154">
-        <v>3.3210000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H154">
-        <v>1</v>
-      </c>
-      <c r="I154">
         <v>0.01</v>
       </c>
     </row>
-    <row r="155" spans="1:9">
+    <row r="155" spans="1:8">
       <c r="A155" t="s">
         <v>7</v>
       </c>
@@ -18792,16 +18322,13 @@
         <v>950</v>
       </c>
       <c r="G155">
-        <v>3.3210000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H155">
-        <v>1</v>
-      </c>
-      <c r="I155">
         <v>0.01</v>
       </c>
     </row>
-    <row r="156" spans="1:9">
+    <row r="156" spans="1:8">
       <c r="A156" t="s">
         <v>7</v>
       </c>
@@ -18821,16 +18348,13 @@
         <v>700</v>
       </c>
       <c r="G156">
-        <v>8.796E-3</v>
+        <v>1</v>
       </c>
       <c r="H156">
-        <v>1</v>
-      </c>
-      <c r="I156">
         <v>0.01</v>
       </c>
     </row>
-    <row r="157" spans="1:9">
+    <row r="157" spans="1:8">
       <c r="A157" t="s">
         <v>7</v>
       </c>
@@ -18850,16 +18374,13 @@
         <v>700</v>
       </c>
       <c r="G157">
-        <v>8.796E-3</v>
+        <v>1</v>
       </c>
       <c r="H157">
-        <v>1</v>
-      </c>
-      <c r="I157">
         <v>0.01</v>
       </c>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:8">
       <c r="A158" t="s">
         <v>7</v>
       </c>
@@ -18879,16 +18400,13 @@
         <v>700</v>
       </c>
       <c r="G158">
-        <v>4.8089999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H158">
-        <v>1</v>
-      </c>
-      <c r="I158">
         <v>0.01</v>
       </c>
     </row>
-    <row r="159" spans="1:9">
+    <row r="159" spans="1:8">
       <c r="A159" t="s">
         <v>7</v>
       </c>
@@ -18908,16 +18426,13 @@
         <v>700</v>
       </c>
       <c r="G159">
-        <v>4.8089999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H159">
-        <v>1</v>
-      </c>
-      <c r="I159">
         <v>0.01</v>
       </c>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:8">
       <c r="A160" t="s">
         <v>7</v>
       </c>
@@ -18937,16 +18452,13 @@
         <v>700</v>
       </c>
       <c r="G160">
-        <v>3.813E-3</v>
+        <v>1</v>
       </c>
       <c r="H160">
-        <v>1</v>
-      </c>
-      <c r="I160">
         <v>0.01</v>
       </c>
     </row>
-    <row r="161" spans="1:9">
+    <row r="161" spans="1:8">
       <c r="A161" t="s">
         <v>7</v>
       </c>
@@ -18966,16 +18478,13 @@
         <v>700</v>
       </c>
       <c r="G161">
-        <v>3.813E-3</v>
+        <v>1</v>
       </c>
       <c r="H161">
-        <v>1</v>
-      </c>
-      <c r="I161">
         <v>0.01</v>
       </c>
     </row>
-    <row r="162" spans="1:9">
+    <row r="162" spans="1:8">
       <c r="A162" t="s">
         <v>7</v>
       </c>
@@ -18995,16 +18504,13 @@
         <v>2800</v>
       </c>
       <c r="G162">
-        <v>9.7680000000000006E-3</v>
+        <v>1</v>
       </c>
       <c r="H162">
-        <v>1</v>
-      </c>
-      <c r="I162">
         <v>0.01</v>
       </c>
     </row>
-    <row r="163" spans="1:9">
+    <row r="163" spans="1:8">
       <c r="A163" t="s">
         <v>7</v>
       </c>
@@ -19024,16 +18530,13 @@
         <v>2800</v>
       </c>
       <c r="G163">
-        <v>9.7680000000000006E-3</v>
+        <v>1</v>
       </c>
       <c r="H163">
-        <v>1</v>
-      </c>
-      <c r="I163">
         <v>0.01</v>
       </c>
     </row>
-    <row r="164" spans="1:9">
+    <row r="164" spans="1:8">
       <c r="A164" t="s">
         <v>7</v>
       </c>
@@ -19053,16 +18556,13 @@
         <v>350</v>
       </c>
       <c r="G164">
-        <v>2.5279999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H164">
-        <v>1</v>
-      </c>
-      <c r="I164">
         <v>0.01</v>
       </c>
     </row>
-    <row r="165" spans="1:9">
+    <row r="165" spans="1:8">
       <c r="A165" t="s">
         <v>7</v>
       </c>
@@ -19082,16 +18582,13 @@
         <v>1300</v>
       </c>
       <c r="G165">
-        <v>6.8099999999999996E-4</v>
+        <v>1</v>
       </c>
       <c r="H165">
-        <v>1</v>
-      </c>
-      <c r="I165">
         <v>0.01</v>
       </c>
     </row>
-    <row r="166" spans="1:9">
+    <row r="166" spans="1:8">
       <c r="A166" t="s">
         <v>7</v>
       </c>
@@ -19111,16 +18608,13 @@
         <v>800</v>
       </c>
       <c r="G166">
-        <v>1.603E-3</v>
+        <v>1</v>
       </c>
       <c r="H166">
-        <v>1</v>
-      </c>
-      <c r="I166">
         <v>0.01</v>
       </c>
     </row>
-    <row r="167" spans="1:9">
+    <row r="167" spans="1:8">
       <c r="A167" t="s">
         <v>7</v>
       </c>
@@ -19140,16 +18634,13 @@
         <v>600</v>
       </c>
       <c r="G167">
-        <v>2.137E-3</v>
+        <v>1</v>
       </c>
       <c r="H167">
-        <v>1</v>
-      </c>
-      <c r="I167">
         <v>0.01</v>
       </c>
     </row>
-    <row r="168" spans="1:9">
+    <row r="168" spans="1:8">
       <c r="A168" t="s">
         <v>7</v>
       </c>
@@ -19169,16 +18660,13 @@
         <v>600</v>
       </c>
       <c r="G168">
-        <v>3.9880000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H168">
-        <v>1</v>
-      </c>
-      <c r="I168">
         <v>0.01</v>
       </c>
     </row>
-    <row r="169" spans="1:9">
+    <row r="169" spans="1:8">
       <c r="A169" t="s">
         <v>7</v>
       </c>
@@ -19198,16 +18686,13 @@
         <v>1000</v>
       </c>
       <c r="G169">
-        <v>2.3930000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H169">
-        <v>1</v>
-      </c>
-      <c r="I169">
         <v>0.01</v>
       </c>
     </row>
-    <row r="170" spans="1:9">
+    <row r="170" spans="1:8">
       <c r="A170" t="s">
         <v>7</v>
       </c>
@@ -19227,16 +18712,13 @@
         <v>700</v>
       </c>
       <c r="G170">
-        <v>4.3309999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H170">
-        <v>1</v>
-      </c>
-      <c r="I170">
         <v>0.01</v>
       </c>
     </row>
-    <row r="171" spans="1:9">
+    <row r="171" spans="1:8">
       <c r="A171" t="s">
         <v>7</v>
       </c>
@@ -19256,16 +18738,13 @@
         <v>600</v>
       </c>
       <c r="G171">
-        <v>5.0530000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H171">
-        <v>1</v>
-      </c>
-      <c r="I171">
         <v>0.01</v>
       </c>
     </row>
-    <row r="172" spans="1:9">
+    <row r="172" spans="1:8">
       <c r="A172" t="s">
         <v>7</v>
       </c>
@@ -19285,16 +18764,13 @@
         <v>250</v>
       </c>
       <c r="G172">
-        <v>3.2550000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H172">
-        <v>1</v>
-      </c>
-      <c r="I172">
         <v>0.01</v>
       </c>
     </row>
-    <row r="173" spans="1:9">
+    <row r="173" spans="1:8">
       <c r="A173" t="s">
         <v>7</v>
       </c>
@@ -19314,16 +18790,13 @@
         <v>300</v>
       </c>
       <c r="G173">
-        <v>2.7130000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H173">
-        <v>1</v>
-      </c>
-      <c r="I173">
         <v>0.01</v>
       </c>
     </row>
-    <row r="174" spans="1:9">
+    <row r="174" spans="1:8">
       <c r="A174" t="s">
         <v>7</v>
       </c>
@@ -19343,16 +18816,13 @@
         <v>2145</v>
       </c>
       <c r="G174">
-        <v>4.248E-3</v>
+        <v>1</v>
       </c>
       <c r="H174">
-        <v>1</v>
-      </c>
-      <c r="I174">
         <v>0.01</v>
       </c>
     </row>
-    <row r="175" spans="1:9">
+    <row r="175" spans="1:8">
       <c r="A175" t="s">
         <v>7</v>
       </c>
@@ -19372,16 +18842,13 @@
         <v>2095</v>
       </c>
       <c r="G175">
-        <v>4.3489999999999996E-3</v>
+        <v>1</v>
       </c>
       <c r="H175">
-        <v>1</v>
-      </c>
-      <c r="I175">
         <v>0.01</v>
       </c>
     </row>
-    <row r="176" spans="1:9">
+    <row r="176" spans="1:8">
       <c r="A176" t="s">
         <v>7</v>
       </c>
@@ -19401,16 +18868,13 @@
         <v>1400</v>
       </c>
       <c r="G176">
-        <v>2.7680000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H176">
-        <v>1</v>
-      </c>
-      <c r="I176">
         <v>0.01</v>
       </c>
     </row>
-    <row r="177" spans="1:9">
+    <row r="177" spans="1:8">
       <c r="A177" t="s">
         <v>7</v>
       </c>
@@ -19430,16 +18894,13 @@
         <v>1400</v>
       </c>
       <c r="G177">
-        <v>2.7680000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H177">
-        <v>1</v>
-      </c>
-      <c r="I177">
         <v>0.01</v>
       </c>
     </row>
-    <row r="178" spans="1:9">
+    <row r="178" spans="1:8">
       <c r="A178" t="s">
         <v>7</v>
       </c>
@@ -19459,16 +18920,13 @@
         <v>600</v>
       </c>
       <c r="G178">
-        <v>8.3330000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H178">
-        <v>1</v>
-      </c>
-      <c r="I178">
         <v>0.01</v>
       </c>
     </row>
-    <row r="179" spans="1:9">
+    <row r="179" spans="1:8">
       <c r="A179" t="s">
         <v>7</v>
       </c>
@@ -19488,16 +18946,13 @@
         <v>600</v>
       </c>
       <c r="G179">
-        <v>8.3330000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H179">
-        <v>1</v>
-      </c>
-      <c r="I179">
         <v>0.01</v>
       </c>
     </row>
-    <row r="180" spans="1:9">
+    <row r="180" spans="1:8">
       <c r="A180" t="s">
         <v>7</v>
       </c>
@@ -19517,16 +18972,13 @@
         <v>3300</v>
       </c>
       <c r="G180">
-        <v>2.1359999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H180">
-        <v>1</v>
-      </c>
-      <c r="I180">
         <v>0.01</v>
       </c>
     </row>
-    <row r="181" spans="1:9">
+    <row r="181" spans="1:8">
       <c r="A181" t="s">
         <v>7</v>
       </c>
@@ -19546,16 +18998,13 @@
         <v>3300</v>
       </c>
       <c r="G181">
-        <v>2.1359999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H181">
-        <v>1</v>
-      </c>
-      <c r="I181">
         <v>0.01</v>
       </c>
     </row>
-    <row r="182" spans="1:9">
+    <row r="182" spans="1:8">
       <c r="A182" t="s">
         <v>7</v>
       </c>
@@ -19575,16 +19024,13 @@
         <v>7300</v>
       </c>
       <c r="G182">
-        <v>1.8680000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H182">
-        <v>1</v>
-      </c>
-      <c r="I182">
         <v>0.01</v>
       </c>
     </row>
-    <row r="183" spans="1:9">
+    <row r="183" spans="1:8">
       <c r="A183" t="s">
         <v>7</v>
       </c>
@@ -19604,16 +19050,13 @@
         <v>7300</v>
       </c>
       <c r="G183">
-        <v>1.8680000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H183">
-        <v>1</v>
-      </c>
-      <c r="I183">
         <v>0.01</v>
       </c>
     </row>
-    <row r="184" spans="1:9">
+    <row r="184" spans="1:8">
       <c r="A184" t="s">
         <v>7</v>
       </c>
@@ -19633,16 +19076,13 @@
         <v>6200</v>
       </c>
       <c r="G184">
-        <v>2.679E-3</v>
+        <v>1</v>
       </c>
       <c r="H184">
-        <v>1</v>
-      </c>
-      <c r="I184">
         <v>0.01</v>
       </c>
     </row>
-    <row r="185" spans="1:9">
+    <row r="185" spans="1:8">
       <c r="A185" t="s">
         <v>7</v>
       </c>
@@ -19662,12 +19102,9 @@
         <v>2800</v>
       </c>
       <c r="G185">
-        <v>5.9319999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H185">
-        <v>1</v>
-      </c>
-      <c r="I185">
         <v>0.01</v>
       </c>
     </row>
@@ -19747,22 +19184,22 @@
         <v>69</v>
       </c>
       <c r="O1" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="P1" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="Q1" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>133</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>134</v>
       </c>
       <c r="S1" s="7" t="s">
         <v>70</v>
       </c>
       <c r="T1" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U1" s="7" t="s">
         <v>71</v>
@@ -19807,7 +19244,7 @@
         <v>84</v>
       </c>
       <c r="AI1" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AJ1" s="8" t="s">
         <v>85</v>
@@ -19818,7 +19255,7 @@
     </row>
     <row r="2" spans="1:41">
       <c r="A2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -19827,10 +19264,10 @@
         <v>48</v>
       </c>
       <c r="D2" t="s">
+        <v>128</v>
+      </c>
+      <c r="J2" t="s">
         <v>129</v>
-      </c>
-      <c r="J2" t="s">
-        <v>130</v>
       </c>
       <c r="K2" t="s">
         <v>7</v>
@@ -19890,27 +19327,27 @@
         <v>36.020000000000003</v>
       </c>
       <c r="AM2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AN2" s="35" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AO2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:41">
       <c r="A3" s="40" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B3" s="43">
         <v>1</v>
       </c>
       <c r="C3" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="D3" s="42" t="s">
         <v>198</v>
-      </c>
-      <c r="D3" s="42" t="s">
-        <v>199</v>
       </c>
       <c r="E3" s="41"/>
       <c r="F3" s="41"/>
@@ -19918,7 +19355,7 @@
       <c r="H3" s="41"/>
       <c r="I3" s="41"/>
       <c r="J3" s="41" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K3" s="41" t="s">
         <v>7</v>
@@ -19986,13 +19423,13 @@
       <c r="AJ3" s="41"/>
       <c r="AK3" s="41"/>
       <c r="AM3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AN3" s="35" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AO3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -20024,13 +19461,13 @@
         <v>4</v>
       </c>
       <c r="C1" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="D1" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="D1" s="28" t="s">
-        <v>172</v>
-      </c>
       <c r="E1" s="28" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -20041,10 +19478,10 @@
         <v>2030</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E2" s="31">
         <v>105</v>
@@ -20058,10 +19495,10 @@
         <v>2040</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E3" s="31">
         <v>105</v>
@@ -20103,13 +19540,13 @@
         <v>87</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F1" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="G1" s="29" t="s">
         <v>161</v>
-      </c>
-      <c r="G1" s="29" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -20120,10 +19557,10 @@
         <v>2030</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="32">
@@ -20142,7 +19579,7 @@
         <v>2030</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D3" s="31" t="s">
         <v>34</v>
@@ -20164,10 +19601,10 @@
         <v>2030</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="32">
@@ -20186,10 +19623,10 @@
         <v>2030</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="32">
@@ -20208,7 +19645,7 @@
         <v>2030</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D6" s="31" t="s">
         <v>46</v>
@@ -20230,10 +19667,10 @@
         <v>2030</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="34">
@@ -20252,10 +19689,10 @@
         <v>2030</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="32">
@@ -20274,10 +19711,10 @@
         <v>2030</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="33">
@@ -20296,10 +19733,10 @@
         <v>2030</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="33">
@@ -20318,10 +19755,10 @@
         <v>2030</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F11" s="33">
         <v>10</v>
@@ -20339,10 +19776,10 @@
         <v>2040</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E12" s="31"/>
       <c r="F12" s="32">
@@ -20361,7 +19798,7 @@
         <v>2040</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D13" s="31" t="s">
         <v>34</v>
@@ -20383,10 +19820,10 @@
         <v>2040</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="32">
@@ -20405,10 +19842,10 @@
         <v>2040</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="32">
@@ -20427,7 +19864,7 @@
         <v>2040</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D16" s="31" t="s">
         <v>46</v>
@@ -20449,10 +19886,10 @@
         <v>2040</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E17" s="31"/>
       <c r="F17" s="34">
@@ -20471,10 +19908,10 @@
         <v>2040</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E18" s="31"/>
       <c r="F18" s="32">
@@ -20493,10 +19930,10 @@
         <v>2040</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E19" s="31"/>
       <c r="F19" s="33">
@@ -20515,10 +19952,10 @@
         <v>2040</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E20" s="31"/>
       <c r="F20" s="33">
@@ -20537,10 +19974,10 @@
         <v>2040</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F21" s="33">
         <v>10</v>
@@ -20558,10 +19995,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E22" s="32">
         <v>1</v>
@@ -20601,10 +20038,10 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>58</v>
@@ -20616,33 +20053,33 @@
         <v>89</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B2" t="s">
         <v>201</v>
-      </c>
-      <c r="B2" t="s">
-        <v>202</v>
       </c>
       <c r="C2">
         <v>2030</v>
@@ -20674,7 +20111,7 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
@@ -20847,12 +20284,12 @@
         <v>2400</v>
       </c>
       <c r="L7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -20887,7 +20324,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
@@ -20955,7 +20392,7 @@
         <v>3000</v>
       </c>
       <c r="L10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -21133,7 +20570,7 @@
         <v>3000</v>
       </c>
       <c r="L15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -21521,7 +20958,7 @@
         <v>879</v>
       </c>
       <c r="L26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -21909,7 +21346,7 @@
         <v>2800</v>
       </c>
       <c r="L37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -22264,10 +21701,10 @@
     </row>
     <row r="48" spans="1:12" hidden="1">
       <c r="A48" t="s">
+        <v>200</v>
+      </c>
+      <c r="B48" t="s">
         <v>201</v>
-      </c>
-      <c r="B48" t="s">
-        <v>202</v>
       </c>
       <c r="C48">
         <v>2040</v>
@@ -22299,7 +21736,7 @@
     </row>
     <row r="49" spans="1:12" hidden="1">
       <c r="A49" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B49" t="s">
         <v>9</v>
@@ -22472,12 +21909,12 @@
         <v>4800</v>
       </c>
       <c r="L53" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:12" hidden="1">
       <c r="A54" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B54" t="s">
         <v>9</v>
@@ -22512,7 +21949,7 @@
     </row>
     <row r="55" spans="1:12" hidden="1">
       <c r="A55" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B55" t="s">
         <v>15</v>
@@ -22580,7 +22017,7 @@
         <v>3000</v>
       </c>
       <c r="L56" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="57" spans="1:12" hidden="1">
@@ -22758,7 +22195,7 @@
         <v>3000</v>
       </c>
       <c r="L61" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="62" spans="1:12" hidden="1">
@@ -23146,7 +22583,7 @@
         <v>1879</v>
       </c>
       <c r="L72" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="73" spans="1:12" hidden="1">
@@ -23534,7 +22971,7 @@
         <v>2800</v>
       </c>
       <c r="L83" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="84" spans="1:12" hidden="1">
@@ -23915,10 +23352,10 @@
         <v>90</v>
       </c>
       <c r="B1" s="44" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1" s="44" t="s">
         <v>205</v>
-      </c>
-      <c r="C1" s="44" t="s">
-        <v>206</v>
       </c>
       <c r="D1" s="23" t="s">
         <v>58</v>
@@ -23939,7 +23376,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D2">
         <v>2030</v>
@@ -23957,7 +23394,7 @@
         <v>BEOF-UK00</v>
       </c>
       <c r="B3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
@@ -23981,7 +23418,7 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D4">
         <v>2030</v>
@@ -24002,7 +23439,7 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D5">
         <v>2030</v>
@@ -24041,7 +23478,7 @@
         <v>DKBH-DKE1</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -24065,7 +23502,7 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D8">
         <v>2030</v>
@@ -24083,7 +23520,7 @@
         <v>EEOF-LV00</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -24107,7 +23544,7 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D10">
         <v>2030</v>
@@ -24149,7 +23586,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12">
         <v>2030</v>
@@ -24167,7 +23604,7 @@
         <v>NLLL-UK00</v>
       </c>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
@@ -24212,7 +23649,7 @@
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D15">
         <v>2040</v>
@@ -24230,7 +23667,7 @@
         <v>BEOF-UK00</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
         <v>27</v>
@@ -24254,7 +23691,7 @@
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D17">
         <v>2040</v>
@@ -24275,7 +23712,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D18">
         <v>2040</v>
@@ -24314,7 +23751,7 @@
         <v>DKBH-DKE1</v>
       </c>
       <c r="B20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -24338,7 +23775,7 @@
         <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D21">
         <v>2040</v>
@@ -24356,7 +23793,7 @@
         <v>EEOF-LV00</v>
       </c>
       <c r="B22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
         <v>17</v>
@@ -24380,7 +23817,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D23">
         <v>2040</v>
@@ -24422,7 +23859,7 @@
         <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D25">
         <v>2040</v>
@@ -24440,7 +23877,7 @@
         <v>NLLL-UK00</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
         <v>27</v>
